--- a/Luban/Config/Datas/Levels/L01/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L01/EnemyData.xlsx
@@ -1391,7 +1391,7 @@
         <v>1.1</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>1.10165</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>5.759049999999999</v>
+        <v>11.5181</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>1.10165</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>5.759049999999999</v>
+        <v>11.5181</v>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>1.1033</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>7.599489597780859</v>
+        <v>15.198979</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>1.1033</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>7.599489597780859</v>
+        <v>15.198979</v>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>1.05315</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>4.939668238557559</v>
+        <v>9.879336</v>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>1.10495</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>8.735991494532199</v>
+        <v>17.471983</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>1.10495</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>8.735991494532199</v>
+        <v>17.471983</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>1.054725</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>5.678394471445929</v>
+        <v>11.356789</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>1.1066</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>13.49476582524272</v>
+        <v>26.989532</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>1.1066</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>13.49476582524272</v>
+        <v>26.989532</v>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>1.006</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>21.10581375067961</v>
+        <v>42.211628</v>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>1.0563</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>8.771597786407767</v>
+        <v>17.543196</v>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>1.10825</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>12.3304347826087</v>
+        <v>24.66087</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>1.10825</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>12.3304347826087</v>
+        <v>24.66087</v>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>1.0075</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>19.2848</v>
+        <v>38.5696</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>1.057875</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>8.014782608695652</v>
+        <v>16.029565</v>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>1.009</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>5.882727014218009</v>
+        <v>11.765454</v>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>1.1099</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>13.07272669826224</v>
+        <v>26.145453</v>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>1.1099</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>13.07272669826224</v>
+        <v>26.145453</v>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>1.009</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>20.44574455608215</v>
+        <v>40.891489</v>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>1.05945</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>8.497272353870457</v>
+        <v>16.994545</v>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>1.0105</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>7.10991304188097</v>
+        <v>14.219826</v>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>1.11155</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>15.79980675973549</v>
+        <v>31.599614</v>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>1.11155</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>15.79980675973549</v>
+        <v>31.599614</v>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>1.0105</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>24.71089777222631</v>
+        <v>49.421796</v>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>1.061025</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>10.26987439382807</v>
+        <v>20.539749</v>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>1.012</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>8.381830654962863</v>
+        <v>16.763661</v>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>1.012</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>8.381830654962863</v>
+        <v>16.763661</v>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>1.1132</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>18.62629034436192</v>
+        <v>37.252581</v>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>1.1132</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>18.62629034436192</v>
+        <v>37.252581</v>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>1.012</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>29.13151809858204</v>
+        <v>58.263036</v>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>1.0626</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>12.10708872383525</v>
+        <v>24.214177</v>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>1.0135</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>14.36727147463995</v>
+        <v>28.734543</v>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>1.0135</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>14.36727147463995</v>
+        <v>28.734543</v>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>1.11485</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>31.92726994364433</v>
+        <v>63.85454</v>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>1.11485</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>31.92726994364433</v>
+        <v>63.85454</v>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>1.0135</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>49.93425019185973</v>
+        <v>99.8685</v>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>1.064175</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>20.75272546336882</v>
+        <v>41.505451</v>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>1.1165</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>27.06555671175858</v>
+        <v>54.131113</v>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>1.1165</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>27.06555671175858</v>
+        <v>54.131113</v>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>1.015</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>42.33053069719043</v>
+        <v>84.661061</v>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>1.06575</v>
       </c>
       <c r="D46" s="0" t="n">
-        <v>17.59261186264308</v>
+        <v>35.185224</v>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>0.8119999999999999</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>50.61259105098856</v>
+        <v>101.225182</v>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>1.0165</v>
       </c>
       <c r="D48" s="0" t="n">
-        <v>11.93660937961595</v>
+        <v>23.873219</v>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>1.11815</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>26.52579862136878</v>
+        <v>53.051597</v>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>1.11815</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>26.52579862136878</v>
+        <v>53.051597</v>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>1.0165</v>
       </c>
       <c r="D51" s="0" t="n">
-        <v>41.48634904382077</v>
+        <v>82.97269799999999</v>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>1.067325</v>
       </c>
       <c r="D52" s="0" t="n">
-        <v>17.24176910388971</v>
+        <v>34.483538</v>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>0.8132</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>49.60324342195963</v>
+        <v>99.206487</v>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>1.018</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>13.55799101741522</v>
+        <v>27.115982</v>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>1.018</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>13.55799101741522</v>
+        <v>27.115982</v>
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>1.1198</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>30.12886892758937</v>
+        <v>60.257738</v>
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>1.1198</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>30.12886892758937</v>
+        <v>60.257738</v>
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>1.018</v>
       </c>
       <c r="D58" s="0" t="n">
-        <v>47.12155100274978</v>
+        <v>94.24310199999999</v>
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>1.0689</v>
       </c>
       <c r="D59" s="0" t="n">
-        <v>19.58376480293309</v>
+        <v>39.16753</v>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>0.8144</v>
       </c>
       <c r="D60" s="0" t="n">
-        <v>56.34098489459211</v>
+        <v>112.68197</v>
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>1.0195</v>
       </c>
       <c r="D61" s="0" t="n">
-        <v>15.59042795722392</v>
+        <v>31.180856</v>
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>1.0195</v>
       </c>
       <c r="D62" s="0" t="n">
-        <v>15.59042795722392</v>
+        <v>31.180856</v>
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>1.12145</v>
       </c>
       <c r="D63" s="0" t="n">
-        <v>34.6453954604976</v>
+        <v>69.290791</v>
       </c>
       <c r="E63" s="0" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>1.12145</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>34.6453954604976</v>
+        <v>69.290791</v>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>1.0195</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>54.18539850021824</v>
+        <v>108.370797</v>
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>1.070475</v>
       </c>
       <c r="D66" s="0" t="n">
-        <v>22.51950704932344</v>
+        <v>45.039014</v>
       </c>
       <c r="E66" s="0" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>0.8156000000000001</v>
       </c>
       <c r="D67" s="0" t="n">
-        <v>64.78688951113051</v>
+        <v>129.573779</v>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>1.021</v>
       </c>
       <c r="D68" s="0" t="n">
-        <v>25.72036826732674</v>
+        <v>51.440737</v>
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>1.021</v>
       </c>
       <c r="D69" s="0" t="n">
-        <v>25.72036826732674</v>
+        <v>51.440737</v>
       </c>
       <c r="E69" s="0" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>1.1231</v>
       </c>
       <c r="D70" s="0" t="n">
-        <v>57.15637392739274</v>
+        <v>114.312748</v>
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>1.1231</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>57.15637392739274</v>
+        <v>114.312748</v>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>1.021</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>89.39256882244224</v>
+        <v>178.785138</v>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>1.07205</v>
       </c>
       <c r="D73" s="0" t="n">
-        <v>37.15164305280528</v>
+        <v>74.303286</v>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>0.8168</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>106.8824192442244</v>
+        <v>213.764838</v>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>1.021</v>
       </c>
       <c r="D75" s="0" t="n">
-        <v>89.39256882244224</v>
+        <v>178.785138</v>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>1.12475</v>
       </c>
       <c r="D76" s="0" t="n">
-        <v>55.11700468018721</v>
+        <v>110.234009</v>
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>1.12475</v>
       </c>
       <c r="D77" s="0" t="n">
-        <v>55.11700468018721</v>
+        <v>110.234009</v>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>1.0225</v>
       </c>
       <c r="D78" s="0" t="n">
-        <v>86.2029953198128</v>
+        <v>172.405991</v>
       </c>
       <c r="E78" s="0" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>1.073625</v>
       </c>
       <c r="D79" s="0" t="n">
-        <v>35.82605304212169</v>
+        <v>71.652106</v>
       </c>
       <c r="E79" s="0" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>0.8180000000000001</v>
       </c>
       <c r="D80" s="0" t="n">
-        <v>103.0687987519501</v>
+        <v>206.137598</v>
       </c>
       <c r="E80" s="0" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>1.0225</v>
       </c>
       <c r="D81" s="0" t="n">
-        <v>86.2029953198128</v>
+        <v>172.405991</v>
       </c>
       <c r="E81" s="0" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>1.024</v>
       </c>
       <c r="D82" s="0" t="n">
-        <v>24.1698956780924</v>
+        <v>48.339791</v>
       </c>
       <c r="E82" s="0" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>1.024</v>
       </c>
       <c r="D83" s="0" t="n">
-        <v>24.1698956780924</v>
+        <v>48.339791</v>
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>1.1264</v>
       </c>
       <c r="D84" s="0" t="n">
-        <v>53.71087928464977</v>
+        <v>107.421759</v>
       </c>
       <c r="E84" s="0" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>1.1264</v>
       </c>
       <c r="D85" s="0" t="n">
-        <v>53.71087928464977</v>
+        <v>107.421759</v>
       </c>
       <c r="E85" s="0" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>1.024</v>
       </c>
       <c r="D86" s="0" t="n">
-        <v>84.00381520119224</v>
+        <v>168.00763</v>
       </c>
       <c r="E86" s="0" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>1.0752</v>
       </c>
       <c r="D87" s="0" t="n">
-        <v>34.91207153502235</v>
+        <v>69.82414300000001</v>
       </c>
       <c r="E87" s="0" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>0.8192</v>
       </c>
       <c r="D88" s="0" t="n">
-        <v>100.4393442622951</v>
+        <v>200.878689</v>
       </c>
       <c r="E88" s="0" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>1.024</v>
       </c>
       <c r="D89" s="0" t="n">
-        <v>84.00381520119224</v>
+        <v>168.00763</v>
       </c>
       <c r="E89" s="0" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>1.0255</v>
       </c>
       <c r="D90" s="0" t="n">
-        <v>24.73662634677132</v>
+        <v>49.473253</v>
       </c>
       <c r="E90" s="0" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>1.0255</v>
       </c>
       <c r="D91" s="0" t="n">
-        <v>24.73662634677132</v>
+        <v>49.473253</v>
       </c>
       <c r="E91" s="0" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>1.0255</v>
       </c>
       <c r="D92" s="0" t="n">
-        <v>24.73662634677132</v>
+        <v>49.473253</v>
       </c>
       <c r="E92" s="0" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>1.12805</v>
       </c>
       <c r="D93" s="0" t="n">
-        <v>54.97028077060293</v>
+        <v>109.940562</v>
       </c>
       <c r="E93" s="0" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>1.12805</v>
       </c>
       <c r="D94" s="0" t="n">
-        <v>54.97028077060293</v>
+        <v>109.940562</v>
       </c>
       <c r="E94" s="0" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>1.0255</v>
       </c>
       <c r="D95" s="0" t="n">
-        <v>85.97351912522298</v>
+        <v>171.947038</v>
       </c>
       <c r="E95" s="0" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>1.076775</v>
       </c>
       <c r="D96" s="0" t="n">
-        <v>35.7306825008919</v>
+        <v>71.461365</v>
       </c>
       <c r="E96" s="0" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>0.8204000000000001</v>
       </c>
       <c r="D97" s="0" t="n">
-        <v>102.7944250410275</v>
+        <v>205.58885</v>
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>1.0255</v>
       </c>
       <c r="D98" s="0" t="n">
-        <v>85.97351912522298</v>
+        <v>171.947038</v>
       </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>1.027</v>
       </c>
       <c r="D99" s="0" t="n">
-        <v>27.5088</v>
+        <v>55.0176</v>
       </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>1.027</v>
       </c>
       <c r="D100" s="0" t="n">
-        <v>27.5088</v>
+        <v>55.0176</v>
       </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>1.027</v>
       </c>
       <c r="D101" s="0" t="n">
-        <v>27.5088</v>
+        <v>55.0176</v>
       </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>1.1297</v>
       </c>
       <c r="D102" s="0" t="n">
-        <v>61.13066666666667</v>
+        <v>122.261333</v>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>1.1297</v>
       </c>
       <c r="D103" s="0" t="n">
-        <v>61.13066666666667</v>
+        <v>122.261333</v>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>1.027</v>
       </c>
       <c r="D104" s="0" t="n">
-        <v>95.60836266666668</v>
+        <v>191.216725</v>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>1.07835</v>
       </c>
       <c r="D105" s="0" t="n">
-        <v>39.73493333333334</v>
+        <v>79.46986699999999</v>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>0.8216</v>
       </c>
       <c r="D106" s="0" t="n">
-        <v>114.3143466666667</v>
+        <v>228.628693</v>
       </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>1.027</v>
       </c>
       <c r="D107" s="0" t="n">
-        <v>95.60836266666668</v>
+        <v>191.216725</v>
       </c>
       <c r="E107" s="0" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>1.0285</v>
       </c>
       <c r="D108" s="0" t="n">
-        <v>44.04151023996082</v>
+        <v>88.08302</v>
       </c>
       <c r="E108" s="0" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>1.0285</v>
       </c>
       <c r="D109" s="0" t="n">
-        <v>44.04151023996082</v>
+        <v>88.08302</v>
       </c>
       <c r="E109" s="0" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>1.0285</v>
       </c>
       <c r="D110" s="0" t="n">
-        <v>44.04151023996082</v>
+        <v>88.08302</v>
       </c>
       <c r="E110" s="0" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>1.13135</v>
       </c>
       <c r="D111" s="0" t="n">
-        <v>97.8700227554685</v>
+        <v>195.740046</v>
       </c>
       <c r="E111" s="0" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>1.13135</v>
       </c>
       <c r="D112" s="0" t="n">
-        <v>97.8700227554685</v>
+        <v>195.740046</v>
       </c>
       <c r="E112" s="0" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>1.0285</v>
       </c>
       <c r="D113" s="0" t="n">
-        <v>153.0687155895527</v>
+        <v>306.137431</v>
       </c>
       <c r="E113" s="0" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>1.079925</v>
       </c>
       <c r="D114" s="0" t="n">
-        <v>63.61551479105452</v>
+        <v>127.23103</v>
       </c>
       <c r="E114" s="0" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>0.8228</v>
       </c>
       <c r="D115" s="0" t="n">
-        <v>183.0169425527261</v>
+        <v>366.033885</v>
       </c>
       <c r="E115" s="0" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>1.03</v>
       </c>
       <c r="D116" s="0" t="n">
-        <v>43.05413016270338</v>
+        <v>86.10826</v>
       </c>
       <c r="E116" s="0" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>1.0285</v>
       </c>
       <c r="D117" s="0" t="n">
-        <v>153.0687155895527</v>
+        <v>306.137431</v>
       </c>
       <c r="E117" s="0" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>1.03</v>
       </c>
       <c r="D118" s="0" t="n">
-        <v>43.05413016270338</v>
+        <v>86.10826</v>
       </c>
       <c r="E118" s="0" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>1.133</v>
       </c>
       <c r="D119" s="0" t="n">
-        <v>95.6758448060075</v>
+        <v>191.35169</v>
       </c>
       <c r="E119" s="0" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>1.133</v>
       </c>
       <c r="D120" s="0" t="n">
-        <v>95.6758448060075</v>
+        <v>191.35169</v>
       </c>
       <c r="E120" s="0" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>1.03</v>
       </c>
       <c r="D121" s="0" t="n">
-        <v>149.6370212765957</v>
+        <v>299.274043</v>
       </c>
       <c r="E121" s="0" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>1.0815</v>
       </c>
       <c r="D122" s="0" t="n">
-        <v>62.18929912390488</v>
+        <v>124.378598</v>
       </c>
       <c r="E122" s="0" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>0.8240000000000001</v>
       </c>
       <c r="D123" s="0" t="n">
-        <v>178.9138297872341</v>
+        <v>357.82766</v>
       </c>
       <c r="E123" s="0" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>1.03</v>
       </c>
       <c r="D124" s="0" t="n">
-        <v>149.6370212765957</v>
+        <v>299.274043</v>
       </c>
       <c r="E124" s="0" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>1.0315</v>
       </c>
       <c r="D125" s="0" t="n">
-        <v>42.37771739130435</v>
+        <v>84.75543500000001</v>
       </c>
       <c r="E125" s="0" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>1.0315</v>
       </c>
       <c r="D126" s="0" t="n">
-        <v>42.37771739130435</v>
+        <v>84.75543500000001</v>
       </c>
       <c r="E126" s="0" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>1.0315</v>
       </c>
       <c r="D127" s="0" t="n">
-        <v>42.37771739130435</v>
+        <v>84.75543500000001</v>
       </c>
       <c r="E127" s="0" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>1.13465</v>
       </c>
       <c r="D128" s="0" t="n">
-        <v>94.17270531400966</v>
+        <v>188.345411</v>
       </c>
       <c r="E128" s="0" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>1.13465</v>
       </c>
       <c r="D129" s="0" t="n">
-        <v>94.17270531400966</v>
+        <v>188.345411</v>
       </c>
       <c r="E129" s="0" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>1.0315</v>
       </c>
       <c r="D130" s="0" t="n">
-        <v>147.2861111111111</v>
+        <v>294.572222</v>
       </c>
       <c r="E130" s="0" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>1.083075</v>
       </c>
       <c r="D131" s="0" t="n">
-        <v>61.21225845410628</v>
+        <v>122.424517</v>
       </c>
       <c r="E131" s="0" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>0.8252000000000002</v>
       </c>
       <c r="D132" s="0" t="n">
-        <v>176.1029589371981</v>
+        <v>352.205918</v>
       </c>
       <c r="E132" s="0" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>1.0315</v>
       </c>
       <c r="D133" s="0" t="n">
-        <v>147.2861111111111</v>
+        <v>294.572222</v>
       </c>
       <c r="E133" s="0" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>1.033</v>
       </c>
       <c r="D134" s="0" t="n">
-        <v>41.55674891146589</v>
+        <v>83.11349800000001</v>
       </c>
       <c r="E134" s="0" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>1.033</v>
       </c>
       <c r="D135" s="0" t="n">
-        <v>41.55674891146589</v>
+        <v>83.11349800000001</v>
       </c>
       <c r="E135" s="0" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>1.033</v>
       </c>
       <c r="D136" s="0" t="n">
-        <v>41.55674891146589</v>
+        <v>83.11349800000001</v>
       </c>
       <c r="E136" s="0" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>1.1363</v>
       </c>
       <c r="D137" s="0" t="n">
-        <v>92.34833091436863</v>
+        <v>184.696662</v>
       </c>
       <c r="E137" s="0" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>1.1363</v>
       </c>
       <c r="D138" s="0" t="n">
-        <v>92.34833091436863</v>
+        <v>184.696662</v>
       </c>
       <c r="E138" s="0" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>1.033</v>
       </c>
       <c r="D139" s="0" t="n">
-        <v>144.4327895500726</v>
+        <v>288.865579</v>
       </c>
       <c r="E139" s="0" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>1.08465</v>
       </c>
       <c r="D140" s="0" t="n">
-        <v>60.02641509433962</v>
+        <v>120.05283</v>
       </c>
       <c r="E140" s="0" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>0.8264</v>
       </c>
       <c r="D141" s="0" t="n">
-        <v>172.6913788098693</v>
+        <v>345.382758</v>
       </c>
       <c r="E141" s="0" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>1.033</v>
       </c>
       <c r="D142" s="0" t="n">
-        <v>144.4327895500726</v>
+        <v>288.865579</v>
       </c>
       <c r="E142" s="0" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>1.0345</v>
       </c>
       <c r="D143" s="0" t="n">
-        <v>43.00289381486677</v>
+        <v>86.005788</v>
       </c>
       <c r="E143" s="0" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>1.0345</v>
       </c>
       <c r="D144" s="0" t="n">
-        <v>43.00289381486677</v>
+        <v>86.005788</v>
       </c>
       <c r="E144" s="0" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>1.0345</v>
       </c>
       <c r="D145" s="0" t="n">
-        <v>43.00289381486677</v>
+        <v>86.005788</v>
       </c>
       <c r="E145" s="0" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>1.13795</v>
       </c>
       <c r="D146" s="0" t="n">
-        <v>95.56198625525947</v>
+        <v>191.123973</v>
       </c>
       <c r="E146" s="0" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>1.13795</v>
       </c>
       <c r="D147" s="0" t="n">
-        <v>95.56198625525947</v>
+        <v>191.123973</v>
       </c>
       <c r="E147" s="0" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>1.0345</v>
       </c>
       <c r="D148" s="0" t="n">
-        <v>149.4589465032258</v>
+        <v>298.917893</v>
       </c>
       <c r="E148" s="0" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>1.086225</v>
       </c>
       <c r="D149" s="0" t="n">
-        <v>62.11529106591865</v>
+        <v>124.230582</v>
       </c>
       <c r="E149" s="0" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>0.8276</v>
       </c>
       <c r="D150" s="0" t="n">
-        <v>178.7009142973352</v>
+        <v>357.401829</v>
       </c>
       <c r="E150" s="0" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>1.0345</v>
       </c>
       <c r="D151" s="0" t="n">
-        <v>149.4589465032258</v>
+        <v>298.917893</v>
       </c>
       <c r="E151" s="0" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>1.036</v>
       </c>
       <c r="D152" s="0" t="n">
-        <v>81.09855453100158</v>
+        <v>162.197109</v>
       </c>
       <c r="E152" s="0" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>1.036</v>
       </c>
       <c r="D153" s="0" t="n">
-        <v>81.09855453100158</v>
+        <v>162.197109</v>
       </c>
       <c r="E153" s="0" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>1.036</v>
       </c>
       <c r="D154" s="0" t="n">
-        <v>81.09855453100158</v>
+        <v>162.197109</v>
       </c>
       <c r="E154" s="0" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>1.1396</v>
       </c>
       <c r="D155" s="0" t="n">
-        <v>180.2190100688924</v>
+        <v>360.43802</v>
       </c>
       <c r="E155" s="0" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>1.1396</v>
       </c>
       <c r="D156" s="0" t="n">
-        <v>180.2190100688924</v>
+        <v>360.43802</v>
       </c>
       <c r="E156" s="0" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>1.036</v>
       </c>
       <c r="D157" s="0" t="n">
-        <v>281.8625317477477</v>
+        <v>563.725063</v>
       </c>
       <c r="E157" s="0" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>1.0878</v>
       </c>
       <c r="D158" s="0" t="n">
-        <v>117.1423565447801</v>
+        <v>234.284713</v>
       </c>
       <c r="E158" s="0" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D159" s="0" t="n">
-        <v>337.0095488288288</v>
+        <v>674.019098</v>
       </c>
       <c r="E159" s="0" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>0.777</v>
       </c>
       <c r="D160" s="0" t="n">
-        <v>674.7399736979331</v>
+        <v>1349.479947</v>
       </c>
       <c r="E160" s="0" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>1.036</v>
       </c>
       <c r="D161" s="0" t="n">
-        <v>281.8625317477477</v>
+        <v>563.725063</v>
       </c>
       <c r="E161" s="0" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>1.003</v>
       </c>
       <c r="D162" s="0" t="n">
-        <v>3.419770319001386</v>
+        <v>6.839541</v>
       </c>
       <c r="E162" s="0" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>1.0045</v>
       </c>
       <c r="D163" s="0" t="n">
-        <v>3.93119617253949</v>
+        <v>7.862392</v>
       </c>
       <c r="E163" s="0" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>1.0045</v>
       </c>
       <c r="D164" s="0" t="n">
-        <v>3.93119617253949</v>
+        <v>7.862392</v>
       </c>
       <c r="E164" s="0" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>1.006</v>
       </c>
       <c r="D165" s="0" t="n">
-        <v>6.072644621359224</v>
+        <v>12.145289</v>
       </c>
       <c r="E165" s="0" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>1.006</v>
       </c>
       <c r="D166" s="0" t="n">
-        <v>6.072644621359224</v>
+        <v>12.145289</v>
       </c>
       <c r="E166" s="0" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>1.006</v>
       </c>
       <c r="D167" s="0" t="n">
-        <v>6.072644621359224</v>
+        <v>12.145289</v>
       </c>
       <c r="E167" s="0" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>1.0075</v>
       </c>
       <c r="D168" s="0" t="n">
-        <v>5.548695652173913</v>
+        <v>11.097391</v>
       </c>
       <c r="E168" s="0" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>1.0075</v>
       </c>
       <c r="D169" s="0" t="n">
-        <v>5.548695652173913</v>
+        <v>11.097391</v>
       </c>
       <c r="E169" s="0" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>1.0075</v>
       </c>
       <c r="D170" s="0" t="n">
-        <v>5.548695652173913</v>
+        <v>11.097391</v>
       </c>
       <c r="E170" s="0" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>1.009</v>
       </c>
       <c r="D171" s="0" t="n">
-        <v>5.882727014218009</v>
+        <v>11.765454</v>
       </c>
       <c r="E171" s="0" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>1.009</v>
       </c>
       <c r="D172" s="0" t="n">
-        <v>5.882727014218009</v>
+        <v>11.765454</v>
       </c>
       <c r="E172" s="0" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>1.0105</v>
       </c>
       <c r="D173" s="0" t="n">
-        <v>7.10991304188097</v>
+        <v>14.219826</v>
       </c>
       <c r="E173" s="0" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>1.0105</v>
       </c>
       <c r="D174" s="0" t="n">
-        <v>7.10991304188097</v>
+        <v>14.219826</v>
       </c>
       <c r="E174" s="0" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>1.012</v>
       </c>
       <c r="D175" s="0" t="n">
-        <v>8.381830654962863</v>
+        <v>16.763661</v>
       </c>
       <c r="E175" s="0" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>1.0135</v>
       </c>
       <c r="D176" s="0" t="n">
-        <v>14.36727147463995</v>
+        <v>28.734543</v>
       </c>
       <c r="E176" s="0" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>1.015</v>
       </c>
       <c r="D177" s="0" t="n">
-        <v>12.17950052029136</v>
+        <v>24.359001</v>
       </c>
       <c r="E177" s="0" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>1.015</v>
       </c>
       <c r="D178" s="0" t="n">
-        <v>12.17950052029136</v>
+        <v>24.359001</v>
       </c>
       <c r="E178" s="0" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>1.015</v>
       </c>
       <c r="D179" s="0" t="n">
-        <v>12.17950052029136</v>
+        <v>24.359001</v>
       </c>
       <c r="E179" s="0" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>1.0165</v>
       </c>
       <c r="D180" s="0" t="n">
-        <v>11.93660937961595</v>
+        <v>23.873219</v>
       </c>
       <c r="E180" s="0" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>1.0165</v>
       </c>
       <c r="D181" s="0" t="n">
-        <v>11.93660937961595</v>
+        <v>23.873219</v>
       </c>
       <c r="E181" s="0" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>1.018</v>
       </c>
       <c r="D182" s="0" t="n">
-        <v>13.55799101741522</v>
+        <v>27.115982</v>
       </c>
       <c r="E182" s="0" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>1.0195</v>
       </c>
       <c r="D183" s="0" t="n">
-        <v>15.59042795722392</v>
+        <v>31.180856</v>
       </c>
       <c r="E183" s="0" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>1.021</v>
       </c>
       <c r="D184" s="0" t="n">
-        <v>25.72036826732674</v>
+        <v>51.440737</v>
       </c>
       <c r="E184" s="0" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>1.0225</v>
       </c>
       <c r="D185" s="0" t="n">
-        <v>24.80265210608425</v>
+        <v>49.605304</v>
       </c>
       <c r="E185" s="0" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>1.0225</v>
       </c>
       <c r="D186" s="0" t="n">
-        <v>24.80265210608425</v>
+        <v>49.605304</v>
       </c>
       <c r="E186" s="0" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>1.0225</v>
       </c>
       <c r="D187" s="0" t="n">
-        <v>24.80265210608425</v>
+        <v>49.605304</v>
       </c>
       <c r="E187" s="0" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>1.024</v>
       </c>
       <c r="D188" s="0" t="n">
-        <v>24.1698956780924</v>
+        <v>48.339791</v>
       </c>
       <c r="E188" s="0" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>1.03</v>
       </c>
       <c r="D189" s="0" t="n">
-        <v>43.05413016270338</v>
+        <v>86.10826</v>
       </c>
       <c r="E189" s="0" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>1.0105</v>
       </c>
       <c r="D190" s="0" t="n">
-        <v>7.10991304188097</v>
+        <v>14.219826</v>
       </c>
       <c r="E190" s="0" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>1.012</v>
       </c>
       <c r="D191" s="0" t="n">
-        <v>8.381830654962863</v>
+        <v>16.763661</v>
       </c>
       <c r="E191" s="0" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>1.0135</v>
       </c>
       <c r="D192" s="0" t="n">
-        <v>14.36727147463995</v>
+        <v>28.734543</v>
       </c>
       <c r="E192" s="0" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>1.015</v>
       </c>
       <c r="D193" s="0" t="n">
-        <v>12.17950052029136</v>
+        <v>24.359001</v>
       </c>
       <c r="E193" s="0" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>1.0165</v>
       </c>
       <c r="D194" s="0" t="n">
-        <v>11.93660937961595</v>
+        <v>23.873219</v>
       </c>
       <c r="E194" s="0" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>1.018</v>
       </c>
       <c r="D195" s="0" t="n">
-        <v>13.55799101741522</v>
+        <v>27.115982</v>
       </c>
       <c r="E195" s="0" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>1.018</v>
       </c>
       <c r="D196" s="0" t="n">
-        <v>13.55799101741522</v>
+        <v>27.115982</v>
       </c>
       <c r="E196" s="0" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>1.0195</v>
       </c>
       <c r="D197" s="0" t="n">
-        <v>15.59042795722392</v>
+        <v>31.180856</v>
       </c>
       <c r="E197" s="0" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>1.0195</v>
       </c>
       <c r="D198" s="0" t="n">
-        <v>15.59042795722392</v>
+        <v>31.180856</v>
       </c>
       <c r="E198" s="0" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>1.021</v>
       </c>
       <c r="D199" s="0" t="n">
-        <v>25.72036826732674</v>
+        <v>51.440737</v>
       </c>
       <c r="E199" s="0" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>1.021</v>
       </c>
       <c r="D200" s="0" t="n">
-        <v>25.72036826732674</v>
+        <v>51.440737</v>
       </c>
       <c r="E200" s="0" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>1.0225</v>
       </c>
       <c r="D201" s="0" t="n">
-        <v>24.80265210608425</v>
+        <v>49.605304</v>
       </c>
       <c r="E201" s="0" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>1.0225</v>
       </c>
       <c r="D202" s="0" t="n">
-        <v>24.80265210608425</v>
+        <v>49.605304</v>
       </c>
       <c r="E202" s="0" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>1.024</v>
       </c>
       <c r="D203" s="0" t="n">
-        <v>24.1698956780924</v>
+        <v>48.339791</v>
       </c>
       <c r="E203" s="0" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>1.024</v>
       </c>
       <c r="D204" s="0" t="n">
-        <v>24.1698956780924</v>
+        <v>48.339791</v>
       </c>
       <c r="E204" s="0" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>1.0255</v>
       </c>
       <c r="D205" s="0" t="n">
-        <v>24.73662634677132</v>
+        <v>49.473253</v>
       </c>
       <c r="E205" s="0" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>1.0255</v>
       </c>
       <c r="D206" s="0" t="n">
-        <v>24.73662634677132</v>
+        <v>49.473253</v>
       </c>
       <c r="E206" s="0" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>1.027</v>
       </c>
       <c r="D207" s="0" t="n">
-        <v>27.5088</v>
+        <v>55.0176</v>
       </c>
       <c r="E207" s="0" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>1.027</v>
       </c>
       <c r="D208" s="0" t="n">
-        <v>27.5088</v>
+        <v>55.0176</v>
       </c>
       <c r="E208" s="0" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>1.0285</v>
       </c>
       <c r="D209" s="0" t="n">
-        <v>44.04151023996082</v>
+        <v>88.08302</v>
       </c>
       <c r="E209" s="0" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>1.0285</v>
       </c>
       <c r="D210" s="0" t="n">
-        <v>44.04151023996082</v>
+        <v>88.08302</v>
       </c>
       <c r="E210" s="0" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>1.03</v>
       </c>
       <c r="D211" s="0" t="n">
-        <v>43.05413016270338</v>
+        <v>86.10826</v>
       </c>
       <c r="E211" s="0" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>1.03</v>
       </c>
       <c r="D212" s="0" t="n">
-        <v>43.05413016270338</v>
+        <v>86.10826</v>
       </c>
       <c r="E212" s="0" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>1.0315</v>
       </c>
       <c r="D213" s="0" t="n">
-        <v>42.37771739130435</v>
+        <v>84.75543500000001</v>
       </c>
       <c r="E213" s="0" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>1.0315</v>
       </c>
       <c r="D214" s="0" t="n">
-        <v>42.37771739130435</v>
+        <v>84.75543500000001</v>
       </c>
       <c r="E214" s="0" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>1.033</v>
       </c>
       <c r="D215" s="0" t="n">
-        <v>41.55674891146589</v>
+        <v>83.11349800000001</v>
       </c>
       <c r="E215" s="0" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>1.033</v>
       </c>
       <c r="D216" s="0" t="n">
-        <v>41.55674891146589</v>
+        <v>83.11349800000001</v>
       </c>
       <c r="E216" s="0" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>1.0345</v>
       </c>
       <c r="D217" s="0" t="n">
-        <v>43.00289381486677</v>
+        <v>86.005788</v>
       </c>
       <c r="E217" s="0" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>1.0345</v>
       </c>
       <c r="D218" s="0" t="n">
-        <v>43.00289381486677</v>
+        <v>86.005788</v>
       </c>
       <c r="E218" s="0" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>1.036</v>
       </c>
       <c r="D219" s="0" t="n">
-        <v>81.09855453100158</v>
+        <v>162.197109</v>
       </c>
       <c r="E219" s="0" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>1.036</v>
       </c>
       <c r="D220" s="0" t="n">
-        <v>81.09855453100158</v>
+        <v>162.197109</v>
       </c>
       <c r="E220" s="0" t="inlineStr">
         <is>

--- a/Luban/Config/Datas/Levels/L01/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L01/EnemyData.xlsx
@@ -1391,7 +1391,7 @@
         <v>1.1</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>11</v>
+        <v>8.25</v>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>1.10165</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>11.5181</v>
+        <v>8.638574999999999</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>1.10165</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>11.5181</v>
+        <v>8.638574999999999</v>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>1.1033</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>15.198979</v>
+        <v>11.399234</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>1.1033</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>15.198979</v>
+        <v>11.399234</v>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>1.05315</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>9.879336</v>
+        <v>7.409502</v>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>1.10495</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>17.471983</v>
+        <v>13.103987</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>1.10495</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>17.471983</v>
+        <v>13.103987</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>1.054725</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>11.356789</v>
+        <v>8.517592</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>1.1066</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>26.989532</v>
+        <v>20.242149</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>1.1066</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>26.989532</v>
+        <v>20.242149</v>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>1.006</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>42.211628</v>
+        <v>31.658721</v>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>1.0563</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>17.543196</v>
+        <v>13.157397</v>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>1.10825</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>24.66087</v>
+        <v>18.495652</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>1.10825</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>24.66087</v>
+        <v>18.495652</v>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>1.0075</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>38.5696</v>
+        <v>28.9272</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>1.057875</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>16.029565</v>
+        <v>12.022174</v>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>1.1099</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>26.145453</v>
+        <v>19.60909</v>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>1.1099</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>26.145453</v>
+        <v>19.60909</v>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>1.009</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>40.891489</v>
+        <v>30.668617</v>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>1.05945</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>16.994545</v>
+        <v>12.745909</v>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>1.11155</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>31.599614</v>
+        <v>23.69971</v>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>1.11155</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>31.599614</v>
+        <v>23.69971</v>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>1.0105</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>49.421796</v>
+        <v>37.066347</v>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>1.061025</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>20.539749</v>
+        <v>15.404812</v>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>1.1132</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>37.252581</v>
+        <v>27.939436</v>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>1.1132</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>37.252581</v>
+        <v>27.939436</v>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>1.012</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>58.263036</v>
+        <v>43.697277</v>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>1.0626</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>24.214177</v>
+        <v>18.160633</v>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>1.11485</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>63.85454</v>
+        <v>47.890905</v>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>1.11485</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>63.85454</v>
+        <v>47.890905</v>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>1.0135</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>99.8685</v>
+        <v>74.901375</v>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>1.064175</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>41.505451</v>
+        <v>31.129088</v>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>1.1165</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>54.131113</v>
+        <v>40.598335</v>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>1.1165</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>54.131113</v>
+        <v>40.598335</v>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>1.015</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>84.661061</v>
+        <v>63.495796</v>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>1.06575</v>
       </c>
       <c r="D46" s="0" t="n">
-        <v>35.185224</v>
+        <v>26.388918</v>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>0.8119999999999999</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>101.225182</v>
+        <v>75.918887</v>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>1.11815</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>53.051597</v>
+        <v>39.788698</v>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>1.11815</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>53.051597</v>
+        <v>39.788698</v>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>1.0165</v>
       </c>
       <c r="D51" s="0" t="n">
-        <v>82.97269799999999</v>
+        <v>62.229524</v>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>1.067325</v>
       </c>
       <c r="D52" s="0" t="n">
-        <v>34.483538</v>
+        <v>25.862654</v>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>0.8132</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>99.206487</v>
+        <v>74.404865</v>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>1.1198</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>60.257738</v>
+        <v>45.193303</v>
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>1.1198</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>60.257738</v>
+        <v>45.193303</v>
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>1.018</v>
       </c>
       <c r="D58" s="0" t="n">
-        <v>94.24310199999999</v>
+        <v>70.682327</v>
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>1.0689</v>
       </c>
       <c r="D59" s="0" t="n">
-        <v>39.16753</v>
+        <v>29.375647</v>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>0.8144</v>
       </c>
       <c r="D60" s="0" t="n">
-        <v>112.68197</v>
+        <v>84.511477</v>
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>1.12145</v>
       </c>
       <c r="D63" s="0" t="n">
-        <v>69.290791</v>
+        <v>51.968093</v>
       </c>
       <c r="E63" s="0" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>1.12145</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>69.290791</v>
+        <v>51.968093</v>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>1.0195</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>108.370797</v>
+        <v>81.278098</v>
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>1.070475</v>
       </c>
       <c r="D66" s="0" t="n">
-        <v>45.039014</v>
+        <v>33.779261</v>
       </c>
       <c r="E66" s="0" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>0.8156000000000001</v>
       </c>
       <c r="D67" s="0" t="n">
-        <v>129.573779</v>
+        <v>97.180334</v>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>1.1231</v>
       </c>
       <c r="D70" s="0" t="n">
-        <v>114.312748</v>
+        <v>85.734561</v>
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>1.1231</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>114.312748</v>
+        <v>85.734561</v>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>1.021</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>178.785138</v>
+        <v>134.088853</v>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>1.07205</v>
       </c>
       <c r="D73" s="0" t="n">
-        <v>74.303286</v>
+        <v>55.727465</v>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>0.8168</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>213.764838</v>
+        <v>160.323629</v>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>1.021</v>
       </c>
       <c r="D75" s="0" t="n">
-        <v>178.785138</v>
+        <v>134.088853</v>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>1.12475</v>
       </c>
       <c r="D76" s="0" t="n">
-        <v>110.234009</v>
+        <v>82.675507</v>
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>1.12475</v>
       </c>
       <c r="D77" s="0" t="n">
-        <v>110.234009</v>
+        <v>82.675507</v>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>1.0225</v>
       </c>
       <c r="D78" s="0" t="n">
-        <v>172.405991</v>
+        <v>129.304493</v>
       </c>
       <c r="E78" s="0" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>1.073625</v>
       </c>
       <c r="D79" s="0" t="n">
-        <v>71.652106</v>
+        <v>53.73908</v>
       </c>
       <c r="E79" s="0" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>0.8180000000000001</v>
       </c>
       <c r="D80" s="0" t="n">
-        <v>206.137598</v>
+        <v>154.603198</v>
       </c>
       <c r="E80" s="0" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>1.0225</v>
       </c>
       <c r="D81" s="0" t="n">
-        <v>172.405991</v>
+        <v>129.304493</v>
       </c>
       <c r="E81" s="0" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>1.1264</v>
       </c>
       <c r="D84" s="0" t="n">
-        <v>107.421759</v>
+        <v>80.56631899999999</v>
       </c>
       <c r="E84" s="0" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>1.1264</v>
       </c>
       <c r="D85" s="0" t="n">
-        <v>107.421759</v>
+        <v>80.56631899999999</v>
       </c>
       <c r="E85" s="0" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>1.024</v>
       </c>
       <c r="D86" s="0" t="n">
-        <v>168.00763</v>
+        <v>126.005723</v>
       </c>
       <c r="E86" s="0" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>1.0752</v>
       </c>
       <c r="D87" s="0" t="n">
-        <v>69.82414300000001</v>
+        <v>52.368107</v>
       </c>
       <c r="E87" s="0" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>0.8192</v>
       </c>
       <c r="D88" s="0" t="n">
-        <v>200.878689</v>
+        <v>150.659016</v>
       </c>
       <c r="E88" s="0" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>1.024</v>
       </c>
       <c r="D89" s="0" t="n">
-        <v>168.00763</v>
+        <v>126.005723</v>
       </c>
       <c r="E89" s="0" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>1.12805</v>
       </c>
       <c r="D93" s="0" t="n">
-        <v>109.940562</v>
+        <v>82.455421</v>
       </c>
       <c r="E93" s="0" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>1.12805</v>
       </c>
       <c r="D94" s="0" t="n">
-        <v>109.940562</v>
+        <v>82.455421</v>
       </c>
       <c r="E94" s="0" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>1.0255</v>
       </c>
       <c r="D95" s="0" t="n">
-        <v>171.947038</v>
+        <v>128.960279</v>
       </c>
       <c r="E95" s="0" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>1.076775</v>
       </c>
       <c r="D96" s="0" t="n">
-        <v>71.461365</v>
+        <v>53.596024</v>
       </c>
       <c r="E96" s="0" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>0.8204000000000001</v>
       </c>
       <c r="D97" s="0" t="n">
-        <v>205.58885</v>
+        <v>154.191638</v>
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>1.0255</v>
       </c>
       <c r="D98" s="0" t="n">
-        <v>171.947038</v>
+        <v>128.960279</v>
       </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>1.1297</v>
       </c>
       <c r="D102" s="0" t="n">
-        <v>122.261333</v>
+        <v>91.696</v>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>1.1297</v>
       </c>
       <c r="D103" s="0" t="n">
-        <v>122.261333</v>
+        <v>91.696</v>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>1.027</v>
       </c>
       <c r="D104" s="0" t="n">
-        <v>191.216725</v>
+        <v>143.412544</v>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>1.07835</v>
       </c>
       <c r="D105" s="0" t="n">
-        <v>79.46986699999999</v>
+        <v>59.6024</v>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>0.8216</v>
       </c>
       <c r="D106" s="0" t="n">
-        <v>228.628693</v>
+        <v>171.47152</v>
       </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>1.027</v>
       </c>
       <c r="D107" s="0" t="n">
-        <v>191.216725</v>
+        <v>143.412544</v>
       </c>
       <c r="E107" s="0" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>1.13135</v>
       </c>
       <c r="D111" s="0" t="n">
-        <v>195.740046</v>
+        <v>146.805034</v>
       </c>
       <c r="E111" s="0" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>1.13135</v>
       </c>
       <c r="D112" s="0" t="n">
-        <v>195.740046</v>
+        <v>146.805034</v>
       </c>
       <c r="E112" s="0" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>1.0285</v>
       </c>
       <c r="D113" s="0" t="n">
-        <v>306.137431</v>
+        <v>229.603073</v>
       </c>
       <c r="E113" s="0" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>1.079925</v>
       </c>
       <c r="D114" s="0" t="n">
-        <v>127.23103</v>
+        <v>95.423272</v>
       </c>
       <c r="E114" s="0" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>0.8228</v>
       </c>
       <c r="D115" s="0" t="n">
-        <v>366.033885</v>
+        <v>274.525414</v>
       </c>
       <c r="E115" s="0" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>1.0285</v>
       </c>
       <c r="D117" s="0" t="n">
-        <v>306.137431</v>
+        <v>229.603073</v>
       </c>
       <c r="E117" s="0" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>1.133</v>
       </c>
       <c r="D119" s="0" t="n">
-        <v>191.35169</v>
+        <v>143.513767</v>
       </c>
       <c r="E119" s="0" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>1.133</v>
       </c>
       <c r="D120" s="0" t="n">
-        <v>191.35169</v>
+        <v>143.513767</v>
       </c>
       <c r="E120" s="0" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>1.03</v>
       </c>
       <c r="D121" s="0" t="n">
-        <v>299.274043</v>
+        <v>224.455532</v>
       </c>
       <c r="E121" s="0" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>1.0815</v>
       </c>
       <c r="D122" s="0" t="n">
-        <v>124.378598</v>
+        <v>93.28394900000001</v>
       </c>
       <c r="E122" s="0" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>0.8240000000000001</v>
       </c>
       <c r="D123" s="0" t="n">
-        <v>357.82766</v>
+        <v>268.370745</v>
       </c>
       <c r="E123" s="0" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>1.03</v>
       </c>
       <c r="D124" s="0" t="n">
-        <v>299.274043</v>
+        <v>224.455532</v>
       </c>
       <c r="E124" s="0" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>1.13465</v>
       </c>
       <c r="D128" s="0" t="n">
-        <v>188.345411</v>
+        <v>141.259058</v>
       </c>
       <c r="E128" s="0" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>1.13465</v>
       </c>
       <c r="D129" s="0" t="n">
-        <v>188.345411</v>
+        <v>141.259058</v>
       </c>
       <c r="E129" s="0" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>1.0315</v>
       </c>
       <c r="D130" s="0" t="n">
-        <v>294.572222</v>
+        <v>220.929167</v>
       </c>
       <c r="E130" s="0" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>1.083075</v>
       </c>
       <c r="D131" s="0" t="n">
-        <v>122.424517</v>
+        <v>91.818388</v>
       </c>
       <c r="E131" s="0" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>0.8252000000000002</v>
       </c>
       <c r="D132" s="0" t="n">
-        <v>352.205918</v>
+        <v>264.154438</v>
       </c>
       <c r="E132" s="0" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>1.0315</v>
       </c>
       <c r="D133" s="0" t="n">
-        <v>294.572222</v>
+        <v>220.929167</v>
       </c>
       <c r="E133" s="0" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>1.1363</v>
       </c>
       <c r="D137" s="0" t="n">
-        <v>184.696662</v>
+        <v>138.522496</v>
       </c>
       <c r="E137" s="0" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>1.1363</v>
       </c>
       <c r="D138" s="0" t="n">
-        <v>184.696662</v>
+        <v>138.522496</v>
       </c>
       <c r="E138" s="0" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>1.033</v>
       </c>
       <c r="D139" s="0" t="n">
-        <v>288.865579</v>
+        <v>216.649184</v>
       </c>
       <c r="E139" s="0" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>1.08465</v>
       </c>
       <c r="D140" s="0" t="n">
-        <v>120.05283</v>
+        <v>90.03962300000001</v>
       </c>
       <c r="E140" s="0" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>0.8264</v>
       </c>
       <c r="D141" s="0" t="n">
-        <v>345.382758</v>
+        <v>259.037068</v>
       </c>
       <c r="E141" s="0" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>1.033</v>
       </c>
       <c r="D142" s="0" t="n">
-        <v>288.865579</v>
+        <v>216.649184</v>
       </c>
       <c r="E142" s="0" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>1.13795</v>
       </c>
       <c r="D146" s="0" t="n">
-        <v>191.123973</v>
+        <v>143.342979</v>
       </c>
       <c r="E146" s="0" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>1.13795</v>
       </c>
       <c r="D147" s="0" t="n">
-        <v>191.123973</v>
+        <v>143.342979</v>
       </c>
       <c r="E147" s="0" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>1.0345</v>
       </c>
       <c r="D148" s="0" t="n">
-        <v>298.917893</v>
+        <v>224.18842</v>
       </c>
       <c r="E148" s="0" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>1.086225</v>
       </c>
       <c r="D149" s="0" t="n">
-        <v>124.230582</v>
+        <v>93.172937</v>
       </c>
       <c r="E149" s="0" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>0.8276</v>
       </c>
       <c r="D150" s="0" t="n">
-        <v>357.401829</v>
+        <v>268.051371</v>
       </c>
       <c r="E150" s="0" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>1.0345</v>
       </c>
       <c r="D151" s="0" t="n">
-        <v>298.917893</v>
+        <v>224.18842</v>
       </c>
       <c r="E151" s="0" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>1.1396</v>
       </c>
       <c r="D155" s="0" t="n">
-        <v>360.43802</v>
+        <v>270.328515</v>
       </c>
       <c r="E155" s="0" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>1.1396</v>
       </c>
       <c r="D156" s="0" t="n">
-        <v>360.43802</v>
+        <v>270.328515</v>
       </c>
       <c r="E156" s="0" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>1.036</v>
       </c>
       <c r="D157" s="0" t="n">
-        <v>563.725063</v>
+        <v>422.793798</v>
       </c>
       <c r="E157" s="0" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>1.0878</v>
       </c>
       <c r="D158" s="0" t="n">
-        <v>234.284713</v>
+        <v>175.713535</v>
       </c>
       <c r="E158" s="0" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D159" s="0" t="n">
-        <v>674.019098</v>
+        <v>505.514323</v>
       </c>
       <c r="E159" s="0" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>0.777</v>
       </c>
       <c r="D160" s="0" t="n">
-        <v>1349.479947</v>
+        <v>1012.109961</v>
       </c>
       <c r="E160" s="0" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>1.036</v>
       </c>
       <c r="D161" s="0" t="n">
-        <v>563.725063</v>
+        <v>422.793798</v>
       </c>
       <c r="E161" s="0" t="inlineStr">
         <is>

--- a/Luban/Config/Datas/Levels/L01/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L01/EnemyData.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P220"/>
+  <dimension ref="A1:Q220"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" style="2" min="1" max="1"/>
@@ -1140,6 +1140,7 @@
     <col width="9" customWidth="1" style="2" min="13" max="14"/>
     <col width="17.3333333333333" customWidth="1" style="2" min="15" max="15"/>
     <col width="9" customWidth="1" style="2" min="16" max="16384"/>
+    <col width="10" customWidth="1" style="2" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1223,6 +1224,11 @@
           <t>desc</t>
         </is>
       </c>
+      <c r="Q1" s="0" t="inlineStr">
+        <is>
+          <t>levelId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1272,37 +1278,42 @@
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K2" s="0" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="M2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N2" s="0" t="inlineStr">
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q2" s="0" t="inlineStr">
         <is>
           <t>int</t>
-        </is>
-      </c>
-      <c r="O2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="P2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
         </is>
       </c>
     </row>
@@ -1380,6 +1391,11 @@
       <c r="P3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="Q3" s="0" t="inlineStr">
+        <is>
+          <t>所属关卡 id（本表每关独立一份，2026-10-30 拆分）</t>
         </is>
       </c>
     </row>
@@ -1433,6 +1449,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=1</t>
         </is>
       </c>
+      <c r="Q4" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="0" t="n">
@@ -1484,6 +1503,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=2</t>
         </is>
       </c>
+      <c r="Q5" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="0" t="n">
@@ -1535,6 +1557,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=3</t>
         </is>
       </c>
+      <c r="Q6" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" customFormat="1" s="1">
       <c r="B7" s="0" t="n">
@@ -1586,6 +1611,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=3</t>
         </is>
       </c>
+      <c r="Q7" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" customFormat="1" s="1">
       <c r="B8" s="0" t="n">
@@ -1637,6 +1665,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=4</t>
         </is>
       </c>
+      <c r="Q8" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" customFormat="1" s="1">
       <c r="B9" s="0" t="n">
@@ -1688,6 +1719,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=4</t>
         </is>
       </c>
+      <c r="Q9" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" customFormat="1" s="1">
       <c r="B10" s="0" t="n">
@@ -1697,7 +1731,7 @@
         <v>1.106615</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>26.359103</v>
+        <v>39.538654</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
@@ -1719,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K10" s="0" t="n">
         <v>1</v>
@@ -1736,8 +1770,11 @@
       <c r="O10" s="0" t="n"/>
       <c r="P10" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q10" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="1" s="1">
@@ -1748,7 +1785,7 @@
         <v>1.056314</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>17.133417</v>
+        <v>25.700126</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
@@ -1770,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>4</v>
+        <v>0.1522</v>
       </c>
       <c r="K11" s="0" t="n">
         <v>1</v>
@@ -1787,8 +1824,11 @@
       <c r="O11" s="0" t="n"/>
       <c r="P11" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q11" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1799,7 +1839,7 @@
         <v>1.006014</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>48.500748</v>
+        <v>72.751122</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
@@ -1821,7 +1861,7 @@
         <v>0.08</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K12" s="0" t="n">
         <v>1</v>
@@ -1838,8 +1878,11 @@
       <c r="O12" s="0" t="n"/>
       <c r="P12" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q12" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1850,7 +1893,7 @@
         <v>1.006014</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>42.174564</v>
+        <v>84.34912799999999</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
@@ -1872,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K13" s="0" t="n">
         <v>1</v>
@@ -1889,8 +1932,11 @@
       <c r="O13" s="0" t="n"/>
       <c r="P13" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+        </is>
+      </c>
+      <c r="Q13" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1901,7 +1947,7 @@
         <v>1.108275</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>24.216054</v>
+        <v>36.324081</v>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
@@ -1923,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K14" s="0" t="n">
         <v>1</v>
@@ -1940,8 +1986,11 @@
       <c r="O14" s="0" t="n"/>
       <c r="P14" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q14" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1952,7 +2001,7 @@
         <v>1.057899</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>15.740434</v>
+        <v>23.610651</v>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
@@ -1974,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>3</v>
+        <v>0.1522</v>
       </c>
       <c r="K15" s="0" t="n">
         <v>1</v>
@@ -1991,8 +2040,11 @@
       <c r="O15" s="0" t="n"/>
       <c r="P15" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q15" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2003,7 +2055,7 @@
         <v>1.007523</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>44.557539</v>
+        <v>66.836309</v>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
@@ -2025,7 +2077,7 @@
         <v>0.08</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K16" s="0" t="n">
         <v>1</v>
@@ -2042,8 +2094,11 @@
       <c r="O16" s="0" t="n"/>
       <c r="P16" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q16" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2054,7 +2109,7 @@
         <v>1.007523</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>38.745686</v>
+        <v>77.491372</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
@@ -2076,7 +2131,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>3</v>
+        <v>0.36</v>
       </c>
       <c r="K17" s="0" t="n">
         <v>1</v>
@@ -2093,8 +2148,11 @@
       <c r="O17" s="0" t="n"/>
       <c r="P17" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+        </is>
+      </c>
+      <c r="Q17" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2105,7 +2163,7 @@
         <v>1.109937</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>25.653061</v>
+        <v>38.479591</v>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
@@ -2127,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K18" s="0" t="n">
         <v>1</v>
@@ -2144,8 +2202,11 @@
       <c r="O18" s="0" t="n"/>
       <c r="P18" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | gold20-20261029: reward +20% | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q18" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2156,7 +2217,7 @@
         <v>1.059486</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>16.674491</v>
+        <v>25.011736</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
@@ -2178,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>2</v>
+        <v>0.1522</v>
       </c>
       <c r="K19" s="0" t="n">
         <v>1</v>
@@ -2195,8 +2256,11 @@
       <c r="O19" s="0" t="n"/>
       <c r="P19" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q19" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2207,7 +2271,7 @@
         <v>1.009034</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>47.201633</v>
+        <v>70.802449</v>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
@@ -2229,7 +2293,7 @@
         <v>0.08</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>2</v>
+        <v>0.3045</v>
       </c>
       <c r="K20" s="0" t="n">
         <v>1</v>
@@ -2246,8 +2310,11 @@
       <c r="O20" s="0" t="n"/>
       <c r="P20" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q20" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2258,7 +2325,7 @@
         <v>1.009034</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>41.044898</v>
+        <v>82.08979600000001</v>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
@@ -2280,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>2</v>
+        <v>0.36</v>
       </c>
       <c r="K21" s="0" t="n">
         <v>1</v>
@@ -2297,8 +2364,11 @@
       <c r="O21" s="0" t="n"/>
       <c r="P21" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+        </is>
+      </c>
+      <c r="Q21" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2309,7 +2379,7 @@
         <v>1.111602</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>30.6375</v>
+        <v>45.95625</v>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
@@ -2331,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K22" s="0" t="n">
         <v>1</v>
@@ -2348,8 +2418,11 @@
       <c r="O22" s="0" t="n"/>
       <c r="P22" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q22" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2360,7 +2433,7 @@
         <v>1.061075</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>19.914375</v>
+        <v>29.871562</v>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
@@ -2382,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="0" t="n">
-        <v>2</v>
+        <v>0.1522</v>
       </c>
       <c r="K23" s="0" t="n">
         <v>1</v>
@@ -2399,8 +2472,11 @@
       <c r="O23" s="0" t="n"/>
       <c r="P23" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q23" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2411,7 +2487,7 @@
         <v>1.010547</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>56.373</v>
+        <v>84.5595</v>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
@@ -2433,7 +2509,7 @@
         <v>0.08</v>
       </c>
       <c r="J24" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K24" s="0" t="n">
         <v>1</v>
@@ -2450,8 +2526,11 @@
       <c r="O24" s="0" t="n"/>
       <c r="P24" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q24" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2462,7 +2541,7 @@
         <v>1.010547</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>49.02</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
@@ -2484,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="0" t="n">
-        <v>3</v>
+        <v>0.36</v>
       </c>
       <c r="K25" s="0" t="n">
         <v>1</v>
@@ -2501,8 +2580,11 @@
       <c r="O25" s="0" t="n"/>
       <c r="P25" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+        </is>
+      </c>
+      <c r="Q25" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2513,7 +2595,7 @@
         <v>1.11327</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>36.165802</v>
+        <v>54.248703</v>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
@@ -2535,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K26" s="0" t="n">
         <v>1</v>
@@ -2552,8 +2634,11 @@
       <c r="O26" s="0" t="n"/>
       <c r="P26" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q26" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2564,7 +2649,7 @@
         <v>1.062666</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>23.507772</v>
+        <v>35.261658</v>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
@@ -2586,7 +2671,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K27" s="0" t="n">
         <v>1</v>
@@ -2603,8 +2688,11 @@
       <c r="O27" s="0" t="n"/>
       <c r="P27" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q27" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2615,7 +2703,7 @@
         <v>1.012063</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>66.545078</v>
+        <v>99.817617</v>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
@@ -2637,7 +2725,7 @@
         <v>0.08</v>
       </c>
       <c r="J28" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K28" s="0" t="n">
         <v>1</v>
@@ -2654,8 +2742,11 @@
       <c r="O28" s="0" t="n"/>
       <c r="P28" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q28" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2666,7 +2757,7 @@
         <v>1.012063</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>57.865284</v>
+        <v>115.730568</v>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
@@ -2688,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="0" t="n">
-        <v>5</v>
+        <v>0.36</v>
       </c>
       <c r="K29" s="0" t="n">
         <v>1</v>
@@ -2705,8 +2796,11 @@
       <c r="O29" s="0" t="n"/>
       <c r="P29" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+        </is>
+      </c>
+      <c r="Q29" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2717,7 +2811,7 @@
         <v>1.114939</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>62.217461</v>
+        <v>93.32619099999999</v>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
@@ -2739,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K30" s="0" t="n">
         <v>1</v>
@@ -2756,8 +2850,11 @@
       <c r="O30" s="0" t="n"/>
       <c r="P30" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q30" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2768,7 +2865,7 @@
         <v>1.06426</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>40.44135</v>
+        <v>60.662025</v>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
@@ -2790,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K31" s="0" t="n">
         <v>1</v>
@@ -2807,8 +2904,11 @@
       <c r="O31" s="0" t="n"/>
       <c r="P31" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q31" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2819,7 +2919,7 @@
         <v>1.013581</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>114.480129</v>
+        <v>171.720193</v>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
@@ -2841,7 +2941,7 @@
         <v>0.08</v>
       </c>
       <c r="J32" s="0" t="n">
-        <v>2</v>
+        <v>0.3045</v>
       </c>
       <c r="K32" s="0" t="n">
         <v>1</v>
@@ -2858,8 +2958,11 @@
       <c r="O32" s="0" t="n"/>
       <c r="P32" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q32" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2870,7 +2973,7 @@
         <v>1.013581</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>99.547938</v>
+        <v>199.095876</v>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
@@ -2892,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K33" s="0" t="n">
         <v>1</v>
@@ -2909,8 +3012,11 @@
       <c r="O33" s="0" t="n"/>
       <c r="P33" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+        </is>
+      </c>
+      <c r="Q33" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2921,7 +3027,7 @@
         <v>1.116612</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>47.389912</v>
+        <v>71.084868</v>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
@@ -2943,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K34" s="0" t="n">
         <v>1</v>
@@ -2960,8 +3066,11 @@
       <c r="O34" s="0" t="n"/>
       <c r="P34" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q34" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2972,7 +3081,7 @@
         <v>1.065857</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>30.803444</v>
+        <v>46.205166</v>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
@@ -2994,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K35" s="0" t="n">
         <v>1</v>
@@ -3011,8 +3120,11 @@
       <c r="O35" s="0" t="n"/>
       <c r="P35" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q35" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -3023,7 +3135,7 @@
         <v>1.015102</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>87.19743800000001</v>
+        <v>130.796157</v>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
@@ -3045,7 +3157,7 @@
         <v>0.08</v>
       </c>
       <c r="J36" s="0" t="n">
-        <v>2</v>
+        <v>0.3045</v>
       </c>
       <c r="K36" s="0" t="n">
         <v>1</v>
@@ -3062,8 +3174,11 @@
       <c r="O36" s="0" t="n"/>
       <c r="P36" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q36" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -3074,7 +3189,7 @@
         <v>0.8120810000000001</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>161.125701</v>
+        <v>241.688551</v>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
@@ -3096,7 +3211,7 @@
         <v>0.15</v>
       </c>
       <c r="J37" s="0" t="n">
-        <v>1</v>
+        <v>0.4948</v>
       </c>
       <c r="K37" s="0" t="n">
         <v>2</v>
@@ -3113,8 +3228,11 @@
       <c r="O37" s="0" t="n"/>
       <c r="P37" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+        </is>
+      </c>
+      <c r="Q37" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -3125,7 +3243,7 @@
         <v>1.015102</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>75.82386</v>
+        <v>151.64772</v>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
@@ -3147,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K38" s="0" t="n">
         <v>1</v>
@@ -3164,8 +3282,11 @@
       <c r="O38" s="0" t="n"/>
       <c r="P38" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+        </is>
+      </c>
+      <c r="Q38" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -3176,7 +3297,7 @@
         <v>1.118287</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>45.506493</v>
+        <v>68.259739</v>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
@@ -3198,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K39" s="0" t="n">
         <v>1</v>
@@ -3215,8 +3336,11 @@
       <c r="O39" s="0" t="n"/>
       <c r="P39" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q39" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -3227,7 +3351,7 @@
         <v>1.067456</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>29.579221</v>
+        <v>44.368831</v>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
@@ -3249,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K40" s="0" t="n">
         <v>1</v>
@@ -3266,8 +3390,11 @@
       <c r="O40" s="0" t="n"/>
       <c r="P40" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q40" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -3278,7 +3405,7 @@
         <v>1.016624</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>83.731949</v>
+        <v>125.597924</v>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
@@ -3300,7 +3427,7 @@
         <v>0.08</v>
       </c>
       <c r="J41" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K41" s="0" t="n">
         <v>1</v>
@@ -3317,8 +3444,11 @@
       <c r="O41" s="0" t="n"/>
       <c r="P41" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q41" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -3329,7 +3459,7 @@
         <v>0.813299</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>154.722078</v>
+        <v>232.083117</v>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
@@ -3351,7 +3481,7 @@
         <v>0.15</v>
       </c>
       <c r="J42" s="0" t="n">
-        <v>2</v>
+        <v>0.4948</v>
       </c>
       <c r="K42" s="0" t="n">
         <v>2</v>
@@ -3368,8 +3498,11 @@
       <c r="O42" s="0" t="n"/>
       <c r="P42" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+        </is>
+      </c>
+      <c r="Q42" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -3380,7 +3513,7 @@
         <v>1.016624</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>72.81039</v>
+        <v>145.62078</v>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
@@ -3402,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K43" s="0" t="n">
         <v>1</v>
@@ -3419,8 +3552,11 @@
       <c r="O43" s="0" t="n"/>
       <c r="P43" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+        </is>
+      </c>
+      <c r="Q43" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -3431,7 +3567,7 @@
         <v>1.119964</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>52.198953</v>
+        <v>78.298429</v>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
@@ -3453,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K44" s="0" t="n">
         <v>1</v>
@@ -3470,8 +3606,11 @@
       <c r="O44" s="0" t="n"/>
       <c r="P44" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q44" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -3482,7 +3621,7 @@
         <v>1.069057</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>33.929319</v>
+        <v>50.893979</v>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
@@ -3504,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K45" s="0" t="n">
         <v>1</v>
@@ -3521,8 +3660,11 @@
       <c r="O45" s="0" t="n"/>
       <c r="P45" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q45" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3533,7 +3675,7 @@
         <v>1.018149</v>
       </c>
       <c r="D46" s="0" t="n">
-        <v>96.046074</v>
+        <v>144.069111</v>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
@@ -3555,7 +3697,7 @@
         <v>0.08</v>
       </c>
       <c r="J46" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K46" s="0" t="n">
         <v>1</v>
@@ -3572,8 +3714,11 @@
       <c r="O46" s="0" t="n"/>
       <c r="P46" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q46" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3584,7 +3729,7 @@
         <v>0.814519</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>177.47644</v>
+        <v>266.21466</v>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
@@ -3606,7 +3751,7 @@
         <v>0.15</v>
       </c>
       <c r="J47" s="0" t="n">
-        <v>1</v>
+        <v>0.4948</v>
       </c>
       <c r="K47" s="0" t="n">
         <v>2</v>
@@ -3623,8 +3768,11 @@
       <c r="O47" s="0" t="n"/>
       <c r="P47" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+        </is>
+      </c>
+      <c r="Q47" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3635,7 +3783,7 @@
         <v>1.018149</v>
       </c>
       <c r="D48" s="0" t="n">
-        <v>83.51832400000001</v>
+        <v>167.036648</v>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
@@ -3657,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K48" s="0" t="n">
         <v>1</v>
@@ -3674,8 +3822,11 @@
       <c r="O48" s="0" t="n"/>
       <c r="P48" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+        </is>
+      </c>
+      <c r="Q48" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3686,7 +3837,7 @@
         <v>1.121644</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>60.169887</v>
+        <v>90.25483</v>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
@@ -3708,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K49" s="0" t="n">
         <v>1</v>
@@ -3725,8 +3876,11 @@
       <c r="O49" s="0" t="n"/>
       <c r="P49" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q49" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3737,7 +3891,7 @@
         <v>1.07066</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>39.110427</v>
+        <v>58.665641</v>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
@@ -3759,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K50" s="0" t="n">
         <v>1</v>
@@ -3776,8 +3930,11 @@
       <c r="O50" s="0" t="n"/>
       <c r="P50" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q50" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3788,7 +3945,7 @@
         <v>1.019676</v>
       </c>
       <c r="D51" s="0" t="n">
-        <v>110.712591</v>
+        <v>166.068887</v>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
@@ -3810,7 +3967,7 @@
         <v>0.08</v>
       </c>
       <c r="J51" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K51" s="0" t="n">
         <v>1</v>
@@ -3827,8 +3984,11 @@
       <c r="O51" s="0" t="n"/>
       <c r="P51" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q51" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3839,7 +3999,7 @@
         <v>0.815741</v>
       </c>
       <c r="D52" s="0" t="n">
-        <v>204.577615</v>
+        <v>306.866422</v>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
@@ -3861,7 +4021,7 @@
         <v>0.15</v>
       </c>
       <c r="J52" s="0" t="n">
-        <v>1</v>
+        <v>0.4948</v>
       </c>
       <c r="K52" s="0" t="n">
         <v>2</v>
@@ -3878,8 +4038,11 @@
       <c r="O52" s="0" t="n"/>
       <c r="P52" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+        </is>
+      </c>
+      <c r="Q52" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3890,7 +4053,7 @@
         <v>1.019676</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>96.271818</v>
+        <v>192.543636</v>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
@@ -3912,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K53" s="0" t="n">
         <v>1</v>
@@ -3929,8 +4092,11 @@
       <c r="O53" s="0" t="n"/>
       <c r="P53" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+        </is>
+      </c>
+      <c r="Q53" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3941,7 +4107,7 @@
         <v>1.123327</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>98.57142899999999</v>
+        <v>147.857144</v>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
@@ -3963,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K54" s="0" t="n">
         <v>1</v>
@@ -3980,8 +4146,11 @@
       <c r="O54" s="0" t="n"/>
       <c r="P54" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q54" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3992,7 +4161,7 @@
         <v>1.072266</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>64.07142899999999</v>
+        <v>96.10714299999999</v>
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
@@ -4014,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K55" s="0" t="n">
         <v>1</v>
@@ -4031,8 +4200,11 @@
       <c r="O55" s="0" t="n"/>
       <c r="P55" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q55" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -4043,7 +4215,7 @@
         <v>1.021206</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>181.371429</v>
+        <v>272.057143</v>
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
@@ -4065,7 +4237,7 @@
         <v>0.08</v>
       </c>
       <c r="J56" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K56" s="0" t="n">
         <v>1</v>
@@ -4082,8 +4254,11 @@
       <c r="O56" s="0" t="n"/>
       <c r="P56" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q56" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -4094,7 +4269,7 @@
         <v>0.8169650000000001</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>335.142856</v>
+        <v>502.714284</v>
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
@@ -4116,7 +4291,7 @@
         <v>0.15</v>
       </c>
       <c r="J57" s="0" t="n">
-        <v>1</v>
+        <v>0.4948</v>
       </c>
       <c r="K57" s="0" t="n">
         <v>2</v>
@@ -4133,8 +4308,11 @@
       <c r="O57" s="0" t="n"/>
       <c r="P57" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+        </is>
+      </c>
+      <c r="Q57" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -4145,7 +4323,7 @@
         <v>1.021206</v>
       </c>
       <c r="D58" s="0" t="n">
-        <v>157.714286</v>
+        <v>315.428572</v>
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
@@ -4167,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K58" s="0" t="n">
         <v>1</v>
@@ -4184,8 +4362,11 @@
       <c r="O58" s="0" t="n"/>
       <c r="P58" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+        </is>
+      </c>
+      <c r="Q58" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -4196,7 +4377,7 @@
         <v>1.125012</v>
       </c>
       <c r="D59" s="0" t="n">
-        <v>96.632622</v>
+        <v>144.948933</v>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
@@ -4218,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K59" s="0" t="n">
         <v>1</v>
@@ -4235,8 +4416,11 @@
       <c r="O59" s="0" t="n"/>
       <c r="P59" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q59" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -4247,7 +4431,7 @@
         <v>1.073875</v>
       </c>
       <c r="D60" s="0" t="n">
-        <v>62.811204</v>
+        <v>94.21680600000001</v>
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
@@ -4269,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K60" s="0" t="n">
         <v>1</v>
@@ -4286,8 +4470,11 @@
       <c r="O60" s="0" t="n"/>
       <c r="P60" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q60" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -4298,7 +4485,7 @@
         <v>1.022738</v>
       </c>
       <c r="D61" s="0" t="n">
-        <v>177.804025</v>
+        <v>266.706037</v>
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
@@ -4320,7 +4507,7 @@
         <v>0.08</v>
       </c>
       <c r="J61" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K61" s="0" t="n">
         <v>1</v>
@@ -4337,8 +4524,11 @@
       <c r="O61" s="0" t="n"/>
       <c r="P61" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q61" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -4349,7 +4539,7 @@
         <v>0.81819</v>
       </c>
       <c r="D62" s="0" t="n">
-        <v>328.550916</v>
+        <v>492.826374</v>
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
@@ -4371,7 +4561,7 @@
         <v>0.15</v>
       </c>
       <c r="J62" s="0" t="n">
-        <v>1</v>
+        <v>0.4948</v>
       </c>
       <c r="K62" s="0" t="n">
         <v>2</v>
@@ -4388,8 +4578,11 @@
       <c r="O62" s="0" t="n"/>
       <c r="P62" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+        </is>
+      </c>
+      <c r="Q62" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4400,7 +4593,7 @@
         <v>1.022738</v>
       </c>
       <c r="D63" s="0" t="n">
-        <v>154.612196</v>
+        <v>309.224392</v>
       </c>
       <c r="E63" s="0" t="inlineStr">
         <is>
@@ -4422,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="J63" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K63" s="0" t="n">
         <v>1</v>
@@ -4439,8 +4632,11 @@
       <c r="O63" s="0" t="n"/>
       <c r="P63" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+        </is>
+      </c>
+      <c r="Q63" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4451,7 +4647,7 @@
         <v>1.126699</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>93.02042</v>
+        <v>139.53063</v>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
@@ -4473,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="J64" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K64" s="0" t="n">
         <v>1</v>
@@ -4490,8 +4686,11 @@
       <c r="O64" s="0" t="n"/>
       <c r="P64" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q64" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4502,7 +4701,7 @@
         <v>1.075485</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>60.463273</v>
+        <v>90.694909</v>
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
@@ -4524,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K65" s="0" t="n">
         <v>1</v>
@@ -4541,8 +4740,11 @@
       <c r="O65" s="0" t="n"/>
       <c r="P65" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q65" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4553,7 +4755,7 @@
         <v>1.024272</v>
       </c>
       <c r="D66" s="0" t="n">
-        <v>171.157572</v>
+        <v>256.736358</v>
       </c>
       <c r="E66" s="0" t="inlineStr">
         <is>
@@ -4575,7 +4777,7 @@
         <v>0.08</v>
       </c>
       <c r="J66" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K66" s="0" t="n">
         <v>1</v>
@@ -4592,8 +4794,11 @@
       <c r="O66" s="0" t="n"/>
       <c r="P66" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q66" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4604,7 +4809,7 @@
         <v>0.819418</v>
       </c>
       <c r="D67" s="0" t="n">
-        <v>316.269428</v>
+        <v>474.404142</v>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
@@ -4626,7 +4831,7 @@
         <v>0.15</v>
       </c>
       <c r="J67" s="0" t="n">
-        <v>1</v>
+        <v>0.4948</v>
       </c>
       <c r="K67" s="0" t="n">
         <v>2</v>
@@ -4643,8 +4848,11 @@
       <c r="O67" s="0" t="n"/>
       <c r="P67" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+        </is>
+      </c>
+      <c r="Q67" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4655,7 +4863,7 @@
         <v>1.024272</v>
       </c>
       <c r="D68" s="0" t="n">
-        <v>148.832672</v>
+        <v>297.665344</v>
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
@@ -4677,7 +4885,7 @@
         <v>0</v>
       </c>
       <c r="J68" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K68" s="0" t="n">
         <v>1</v>
@@ -4694,8 +4902,11 @@
       <c r="O68" s="0" t="n"/>
       <c r="P68" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+        </is>
+      </c>
+      <c r="Q68" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4706,7 +4917,7 @@
         <v>1.128389</v>
       </c>
       <c r="D69" s="0" t="n">
-        <v>94.690791</v>
+        <v>142.036187</v>
       </c>
       <c r="E69" s="0" t="inlineStr">
         <is>
@@ -4728,7 +4939,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K69" s="0" t="n">
         <v>1</v>
@@ -4745,8 +4956,11 @@
       <c r="O69" s="0" t="n"/>
       <c r="P69" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q69" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4757,7 +4971,7 @@
         <v>1.077099</v>
       </c>
       <c r="D70" s="0" t="n">
-        <v>61.549014</v>
+        <v>92.323521</v>
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
@@ -4779,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K70" s="0" t="n">
         <v>1</v>
@@ -4796,8 +5010,11 @@
       <c r="O70" s="0" t="n"/>
       <c r="P70" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q70" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4808,7 +5025,7 @@
         <v>1.025808</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>174.231055</v>
+        <v>261.346583</v>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
@@ -4830,7 +5047,7 @@
         <v>0.08</v>
       </c>
       <c r="J71" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K71" s="0" t="n">
         <v>1</v>
@@ -4847,8 +5064,11 @@
       <c r="O71" s="0" t="n"/>
       <c r="P71" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q71" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4859,7 +5079,7 @@
         <v>0.820647</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>321.94869</v>
+        <v>482.923035</v>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
@@ -4881,7 +5101,7 @@
         <v>0.15</v>
       </c>
       <c r="J72" s="0" t="n">
-        <v>1</v>
+        <v>0.4948</v>
       </c>
       <c r="K72" s="0" t="n">
         <v>2</v>
@@ -4898,8 +5118,11 @@
       <c r="O72" s="0" t="n"/>
       <c r="P72" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+        </is>
+      </c>
+      <c r="Q72" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4910,7 +5133,7 @@
         <v>1.025808</v>
       </c>
       <c r="D73" s="0" t="n">
-        <v>151.505266</v>
+        <v>303.010532</v>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
@@ -4932,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K73" s="0" t="n">
         <v>1</v>
@@ -4949,8 +5172,11 @@
       <c r="O73" s="0" t="n"/>
       <c r="P73" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+        </is>
+      </c>
+      <c r="Q73" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +5187,7 @@
         <v>1.130082</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>105.966606</v>
+        <v>158.949909</v>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
@@ -4983,7 +5209,7 @@
         <v>0</v>
       </c>
       <c r="J74" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K74" s="0" t="n">
         <v>1</v>
@@ -5000,8 +5226,11 @@
       <c r="O74" s="0" t="n"/>
       <c r="P74" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q74" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -5012,7 +5241,7 @@
         <v>1.078714</v>
       </c>
       <c r="D75" s="0" t="n">
-        <v>68.87829499999999</v>
+        <v>103.317442</v>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
@@ -5034,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="J75" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K75" s="0" t="n">
         <v>1</v>
@@ -5051,8 +5280,11 @@
       <c r="O75" s="0" t="n"/>
       <c r="P75" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q75" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -5063,7 +5295,7 @@
         <v>1.027347</v>
       </c>
       <c r="D76" s="0" t="n">
-        <v>194.978555</v>
+        <v>292.467832</v>
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
@@ -5085,7 +5317,7 @@
         <v>0.08</v>
       </c>
       <c r="J76" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K76" s="0" t="n">
         <v>1</v>
@@ -5102,8 +5334,11 @@
       <c r="O76" s="0" t="n"/>
       <c r="P76" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q76" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -5114,7 +5349,7 @@
         <v>0.821878</v>
       </c>
       <c r="D77" s="0" t="n">
-        <v>360.28646</v>
+        <v>540.4296900000001</v>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
@@ -5136,7 +5371,7 @@
         <v>0.15</v>
       </c>
       <c r="J77" s="0" t="n">
-        <v>1</v>
+        <v>0.4948</v>
       </c>
       <c r="K77" s="0" t="n">
         <v>2</v>
@@ -5153,8 +5388,11 @@
       <c r="O77" s="0" t="n"/>
       <c r="P77" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+        </is>
+      </c>
+      <c r="Q77" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -5165,7 +5403,7 @@
         <v>1.027347</v>
       </c>
       <c r="D78" s="0" t="n">
-        <v>169.54657</v>
+        <v>339.09314</v>
       </c>
       <c r="E78" s="0" t="inlineStr">
         <is>
@@ -5187,7 +5425,7 @@
         <v>0</v>
       </c>
       <c r="J78" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K78" s="0" t="n">
         <v>1</v>
@@ -5204,8 +5442,11 @@
       <c r="O78" s="0" t="n"/>
       <c r="P78" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+        </is>
+      </c>
+      <c r="Q78" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -5216,7 +5457,7 @@
         <v>1.131777</v>
       </c>
       <c r="D79" s="0" t="n">
-        <v>169.228289</v>
+        <v>196.383942</v>
       </c>
       <c r="E79" s="0" t="inlineStr">
         <is>
@@ -5238,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="J79" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K79" s="0" t="n">
         <v>1</v>
@@ -5255,8 +5496,11 @@
       <c r="O79" s="0" t="n"/>
       <c r="P79" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | w20soften-20261029: hp x0.7736 | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q79" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -5267,7 +5511,7 @@
         <v>1.080332</v>
       </c>
       <c r="D80" s="0" t="n">
-        <v>109.998387</v>
+        <v>127.649561</v>
       </c>
       <c r="E80" s="0" t="inlineStr">
         <is>
@@ -5289,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="J80" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K80" s="0" t="n">
         <v>1</v>
@@ -5306,8 +5550,11 @@
       <c r="O80" s="0" t="n"/>
       <c r="P80" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | w20soften-20261029: hp x0.7736 | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q80" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5318,7 +5565,7 @@
         <v>1.028888</v>
       </c>
       <c r="D81" s="0" t="n">
-        <v>311.38005</v>
+        <v>361.346452</v>
       </c>
       <c r="E81" s="0" t="inlineStr">
         <is>
@@ -5340,7 +5587,7 @@
         <v>0.08</v>
       </c>
       <c r="J81" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K81" s="0" t="n">
         <v>1</v>
@@ -5357,8 +5604,11 @@
       <c r="O81" s="0" t="n"/>
       <c r="P81" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | w20soften-20261029: hp x0.7736 | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q81" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5369,7 +5619,7 @@
         <v>0.82311</v>
       </c>
       <c r="D82" s="0" t="n">
-        <v>575.376178</v>
+        <v>667.7053990000001</v>
       </c>
       <c r="E82" s="0" t="inlineStr">
         <is>
@@ -5391,7 +5641,7 @@
         <v>0.15</v>
       </c>
       <c r="J82" s="0" t="n">
-        <v>1</v>
+        <v>0.4948</v>
       </c>
       <c r="K82" s="0" t="n">
         <v>2</v>
@@ -5408,8 +5658,11 @@
       <c r="O82" s="0" t="n"/>
       <c r="P82" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | w20soften-20261029: hp x0.7736 | econneutral-20261030: 0.4948 (was 0.52)</t>
+        </is>
+      </c>
+      <c r="Q82" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5420,7 +5673,7 @@
         <v>1.028888</v>
       </c>
       <c r="D83" s="0" t="n">
-        <v>270.76526</v>
+        <v>418.952407</v>
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
@@ -5442,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K83" s="0" t="n">
         <v>1</v>
@@ -5459,8 +5712,11 @@
       <c r="O83" s="0" t="n"/>
       <c r="P83" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | w20soften-20261029: hp x0.7736</t>
+        </is>
+      </c>
+      <c r="Q83" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5471,7 +5727,7 @@
         <v>1.133475</v>
       </c>
       <c r="D84" s="0" t="n">
-        <v>166.969043</v>
+        <v>250.453564</v>
       </c>
       <c r="E84" s="0" t="inlineStr">
         <is>
@@ -5493,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K84" s="0" t="n">
         <v>1</v>
@@ -5510,8 +5766,11 @@
       <c r="O84" s="0" t="n"/>
       <c r="P84" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q84" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -5522,7 +5781,7 @@
         <v>1.081953</v>
       </c>
       <c r="D85" s="0" t="n">
-        <v>108.529878</v>
+        <v>162.794817</v>
       </c>
       <c r="E85" s="0" t="inlineStr">
         <is>
@@ -5544,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K85" s="0" t="n">
         <v>1</v>
@@ -5561,8 +5820,11 @@
       <c r="O85" s="0" t="n"/>
       <c r="P85" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q85" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5573,7 +5835,7 @@
         <v>1.030431</v>
       </c>
       <c r="D86" s="0" t="n">
-        <v>307.223039</v>
+        <v>460.834559</v>
       </c>
       <c r="E86" s="0" t="inlineStr">
         <is>
@@ -5595,7 +5857,7 @@
         <v>0.08</v>
       </c>
       <c r="J86" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K86" s="0" t="n">
         <v>1</v>
@@ -5612,8 +5874,11 @@
       <c r="O86" s="0" t="n"/>
       <c r="P86" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q86" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -5624,7 +5889,7 @@
         <v>0.824345</v>
       </c>
       <c r="D87" s="0" t="n">
-        <v>567.694745</v>
+        <v>851.542118</v>
       </c>
       <c r="E87" s="0" t="inlineStr">
         <is>
@@ -5646,7 +5911,7 @@
         <v>0.15</v>
       </c>
       <c r="J87" s="0" t="n">
-        <v>1</v>
+        <v>0.4948</v>
       </c>
       <c r="K87" s="0" t="n">
         <v>2</v>
@@ -5663,8 +5928,11 @@
       <c r="O87" s="0" t="n"/>
       <c r="P87" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+        </is>
+      </c>
+      <c r="Q87" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5675,7 +5943,7 @@
         <v>1.030431</v>
       </c>
       <c r="D88" s="0" t="n">
-        <v>267.150468</v>
+        <v>507.585889</v>
       </c>
       <c r="E88" s="0" t="inlineStr">
         <is>
@@ -5697,7 +5965,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K88" s="0" t="n">
         <v>1</v>
@@ -5714,8 +5982,11 @@
       <c r="O88" s="0" t="n"/>
       <c r="P88" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95</t>
+        </is>
+      </c>
+      <c r="Q88" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -5726,7 +5997,7 @@
         <v>1.135175</v>
       </c>
       <c r="D89" s="0" t="n">
-        <v>162.917145</v>
+        <v>244.375718</v>
       </c>
       <c r="E89" s="0" t="inlineStr">
         <is>
@@ -5748,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="J89" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K89" s="0" t="n">
         <v>1</v>
@@ -5765,8 +6036,11 @@
       <c r="O89" s="0" t="n"/>
       <c r="P89" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q89" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -5777,7 +6051,7 @@
         <v>1.083576</v>
       </c>
       <c r="D90" s="0" t="n">
-        <v>105.896144</v>
+        <v>158.844216</v>
       </c>
       <c r="E90" s="0" t="inlineStr">
         <is>
@@ -5799,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="J90" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K90" s="0" t="n">
         <v>1</v>
@@ -5816,8 +6090,11 @@
       <c r="O90" s="0" t="n"/>
       <c r="P90" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q90" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -5828,7 +6105,7 @@
         <v>1.031977</v>
       </c>
       <c r="D91" s="0" t="n">
-        <v>299.767546</v>
+        <v>449.651319</v>
       </c>
       <c r="E91" s="0" t="inlineStr">
         <is>
@@ -5850,7 +6127,7 @@
         <v>0.08</v>
       </c>
       <c r="J91" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K91" s="0" t="n">
         <v>1</v>
@@ -5867,8 +6144,11 @@
       <c r="O91" s="0" t="n"/>
       <c r="P91" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q91" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -5879,7 +6159,7 @@
         <v>0.825582</v>
       </c>
       <c r="D92" s="0" t="n">
-        <v>553.9182929999999</v>
+        <v>830.877439</v>
       </c>
       <c r="E92" s="0" t="inlineStr">
         <is>
@@ -5901,7 +6181,7 @@
         <v>0.15</v>
       </c>
       <c r="J92" s="0" t="n">
-        <v>1</v>
+        <v>0.4948</v>
       </c>
       <c r="K92" s="0" t="n">
         <v>2</v>
@@ -5918,8 +6198,11 @@
       <c r="O92" s="0" t="n"/>
       <c r="P92" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+        </is>
+      </c>
+      <c r="Q92" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -5930,7 +6213,7 @@
         <v>1.031977</v>
       </c>
       <c r="D93" s="0" t="n">
-        <v>260.667432</v>
+        <v>495.268121</v>
       </c>
       <c r="E93" s="0" t="inlineStr">
         <is>
@@ -5952,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K93" s="0" t="n">
         <v>1</v>
@@ -5969,8 +6252,11 @@
       <c r="O93" s="0" t="n"/>
       <c r="P93" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95</t>
+        </is>
+      </c>
+      <c r="Q93" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -5981,7 +6267,7 @@
         <v>1.136877</v>
       </c>
       <c r="D94" s="0" t="n">
-        <v>159.713277</v>
+        <v>239.569916</v>
       </c>
       <c r="E94" s="0" t="inlineStr">
         <is>
@@ -6003,7 +6289,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K94" s="0" t="n">
         <v>1</v>
@@ -6020,8 +6306,11 @@
       <c r="O94" s="0" t="n"/>
       <c r="P94" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q94" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -6032,7 +6321,7 @@
         <v>1.085201</v>
       </c>
       <c r="D95" s="0" t="n">
-        <v>103.81363</v>
+        <v>155.720445</v>
       </c>
       <c r="E95" s="0" t="inlineStr">
         <is>
@@ -6054,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K95" s="0" t="n">
         <v>1</v>
@@ -6071,8 +6360,11 @@
       <c r="O95" s="0" t="n"/>
       <c r="P95" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q95" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -6083,7 +6375,7 @@
         <v>1.033525</v>
       </c>
       <c r="D96" s="0" t="n">
-        <v>293.872431</v>
+        <v>440.808647</v>
       </c>
       <c r="E96" s="0" t="inlineStr">
         <is>
@@ -6105,7 +6397,7 @@
         <v>0.08</v>
       </c>
       <c r="J96" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K96" s="0" t="n">
         <v>1</v>
@@ -6122,8 +6414,11 @@
       <c r="O96" s="0" t="n"/>
       <c r="P96" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q96" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -6134,7 +6429,7 @@
         <v>0.82682</v>
       </c>
       <c r="D97" s="0" t="n">
-        <v>543.025143</v>
+        <v>814.5377140000001</v>
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
@@ -6156,7 +6451,7 @@
         <v>0.15</v>
       </c>
       <c r="J97" s="0" t="n">
-        <v>1</v>
+        <v>0.4948</v>
       </c>
       <c r="K97" s="0" t="n">
         <v>2</v>
@@ -6173,8 +6468,11 @@
       <c r="O97" s="0" t="n"/>
       <c r="P97" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+        </is>
+      </c>
+      <c r="Q97" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -6185,7 +6483,7 @@
         <v>1.033525</v>
       </c>
       <c r="D98" s="0" t="n">
-        <v>255.541244</v>
+        <v>485.528364</v>
       </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
@@ -6207,7 +6505,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K98" s="0" t="n">
         <v>1</v>
@@ -6224,8 +6522,11 @@
       <c r="O98" s="0" t="n"/>
       <c r="P98" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95</t>
+        </is>
+      </c>
+      <c r="Q98" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -6236,7 +6537,7 @@
         <v>1.138583</v>
       </c>
       <c r="D99" s="0" t="n">
-        <v>165.947334</v>
+        <v>248.921001</v>
       </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
@@ -6258,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="J99" s="0" t="n">
-        <v>1</v>
+        <v>0.190875</v>
       </c>
       <c r="K99" s="0" t="n">
         <v>1</v>
@@ -6275,8 +6576,11 @@
       <c r="O99" s="0" t="n"/>
       <c r="P99" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | gold20-20261029: reward +20% | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1909 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q99" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -6287,7 +6591,7 @@
         <v>1.086829</v>
       </c>
       <c r="D100" s="0" t="n">
-        <v>107.865768</v>
+        <v>161.798652</v>
       </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
@@ -6309,7 +6613,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K100" s="0" t="n">
         <v>1</v>
@@ -6326,8 +6630,11 @@
       <c r="O100" s="0" t="n"/>
       <c r="P100" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q100" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -6338,7 +6645,7 @@
         <v>1.035075</v>
       </c>
       <c r="D101" s="0" t="n">
-        <v>305.343096</v>
+        <v>458.014644</v>
       </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
@@ -6360,7 +6667,7 @@
         <v>0.08</v>
       </c>
       <c r="J101" s="0" t="n">
-        <v>2</v>
+        <v>0.3045</v>
       </c>
       <c r="K101" s="0" t="n">
         <v>1</v>
@@ -6377,8 +6684,11 @@
       <c r="O101" s="0" t="n"/>
       <c r="P101" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q101" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -6389,7 +6699,7 @@
         <v>0.82806</v>
       </c>
       <c r="D102" s="0" t="n">
-        <v>564.220938</v>
+        <v>846.331407</v>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
@@ -6411,7 +6721,7 @@
         <v>0.15</v>
       </c>
       <c r="J102" s="0" t="n">
-        <v>1</v>
+        <v>0.4948</v>
       </c>
       <c r="K102" s="0" t="n">
         <v>2</v>
@@ -6428,8 +6738,11 @@
       <c r="O102" s="0" t="n"/>
       <c r="P102" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+        </is>
+      </c>
+      <c r="Q102" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -6440,7 +6753,7 @@
         <v>1.035075</v>
       </c>
       <c r="D103" s="0" t="n">
-        <v>265.515736</v>
+        <v>504.479898</v>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
@@ -6462,7 +6775,7 @@
         <v>0</v>
       </c>
       <c r="J103" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K103" s="0" t="n">
         <v>1</v>
@@ -6479,8 +6792,11 @@
       <c r="O103" s="0" t="n"/>
       <c r="P103" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95</t>
+        </is>
+      </c>
+      <c r="Q103" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -6491,7 +6807,7 @@
         <v>1.140291</v>
       </c>
       <c r="D104" s="0" t="n">
-        <v>285.756233</v>
+        <v>342.907479</v>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
@@ -6513,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="J104" s="0" t="n">
-        <v>1</v>
+        <v>0.1903</v>
       </c>
       <c r="K104" s="0" t="n">
         <v>1</v>
@@ -6530,8 +6846,11 @@
       <c r="O104" s="0" t="n"/>
       <c r="P104" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.1903 (was 0.20)</t>
+        </is>
+      </c>
+      <c r="Q104" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -6542,7 +6861,7 @@
         <v>1.088459</v>
       </c>
       <c r="D105" s="0" t="n">
-        <v>185.741552</v>
+        <v>222.889862</v>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
@@ -6564,7 +6883,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="0" t="n">
-        <v>1</v>
+        <v>0.1522</v>
       </c>
       <c r="K105" s="0" t="n">
         <v>1</v>
@@ -6581,8 +6900,11 @@
       <c r="O105" s="0" t="n"/>
       <c r="P105" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.1522 (was 0.16)</t>
+        </is>
+      </c>
+      <c r="Q105" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -6593,7 +6915,7 @@
         <v>1.036628</v>
       </c>
       <c r="D106" s="0" t="n">
-        <v>525.791467</v>
+        <v>630.949761</v>
       </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
@@ -6615,7 +6937,7 @@
         <v>0.08</v>
       </c>
       <c r="J106" s="0" t="n">
-        <v>1</v>
+        <v>0.3045</v>
       </c>
       <c r="K106" s="0" t="n">
         <v>1</v>
@@ -6632,8 +6954,11 @@
       <c r="O106" s="0" t="n"/>
       <c r="P106" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.3045 (was 0.32)</t>
+        </is>
+      </c>
+      <c r="Q106" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -6644,7 +6969,7 @@
         <v>0.829302</v>
       </c>
       <c r="D107" s="0" t="n">
-        <v>971.57119</v>
+        <v>1165.885428</v>
       </c>
       <c r="E107" s="0" t="inlineStr">
         <is>
@@ -6666,7 +6991,7 @@
         <v>0.15</v>
       </c>
       <c r="J107" s="0" t="n">
-        <v>1</v>
+        <v>0.4948</v>
       </c>
       <c r="K107" s="0" t="n">
         <v>2</v>
@@ -6683,8 +7008,11 @@
       <c r="O107" s="0" t="n"/>
       <c r="P107" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.4948 (was 0.52)</t>
+        </is>
+      </c>
+      <c r="Q107" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -6695,7 +7023,7 @@
         <v>0.777471</v>
       </c>
       <c r="D108" s="0" t="n">
-        <v>1560.229031</v>
+        <v>1872.274838</v>
       </c>
       <c r="E108" s="0" t="inlineStr">
         <is>
@@ -6717,7 +7045,7 @@
         <v>0.22</v>
       </c>
       <c r="J108" s="0" t="n">
-        <v>1</v>
+        <v>1.3322</v>
       </c>
       <c r="K108" s="0" t="n">
         <v>2</v>
@@ -6734,8 +7062,11 @@
       <c r="O108" s="0" t="n"/>
       <c r="P108" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=123; role=elite; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=123; role=elite; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 1.40/只(角色=elite) | w25soften-20261030: hp x0.80 | econneutral-20261030: 1.3322 (was 1.40)</t>
+        </is>
+      </c>
+      <c r="Q108" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -6746,7 +7077,7 @@
         <v>1.036628</v>
       </c>
       <c r="D109" s="0" t="n">
-        <v>457.209972</v>
+        <v>694.959158</v>
       </c>
       <c r="E109" s="0" t="inlineStr">
         <is>
@@ -6768,7 +7099,7 @@
         <v>0</v>
       </c>
       <c r="J109" s="0" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="K109" s="0" t="n">
         <v>1</v>
@@ -6785,8 +7116,11 @@
       <c r="O109" s="0" t="n"/>
       <c r="P109" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x2.0, reward per-wave budget</t>
-        </is>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95 | w25soften-20261030: hp x0.80</t>
+        </is>
+      </c>
+      <c r="Q109" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="110">

--- a/Luban/Config/Datas/Levels/L01/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L01/EnemyData.xlsx
@@ -1731,7 +1731,7 @@
         <v>1.106615</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>39.538654</v>
+        <v>76.606143</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
       <c r="O10" s="0" t="n"/>
       <c r="P10" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55)</t>
         </is>
       </c>
       <c r="Q10" s="0" t="n">
@@ -1785,7 +1785,7 @@
         <v>1.056314</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>25.700126</v>
+        <v>49.793995</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       <c r="O11" s="0" t="n"/>
       <c r="P11" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55)</t>
         </is>
       </c>
       <c r="Q11" s="0" t="n">
@@ -1839,7 +1839,7 @@
         <v>1.006014</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>72.751122</v>
+        <v>140.955298</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
       <c r="O12" s="0" t="n"/>
       <c r="P12" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55)</t>
         </is>
       </c>
       <c r="Q12" s="0" t="n">
@@ -1893,7 +1893,7 @@
         <v>1.006014</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>84.34912799999999</v>
+        <v>92.994913</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       <c r="O13" s="0" t="n"/>
       <c r="P13" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=5 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q13" s="0" t="n">
@@ -1947,7 +1947,7 @@
         <v>1.108275</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>36.324081</v>
+        <v>70.37790699999999</v>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
       <c r="O14" s="0" t="n"/>
       <c r="P14" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55)</t>
         </is>
       </c>
       <c r="Q14" s="0" t="n">
@@ -2001,7 +2001,7 @@
         <v>1.057899</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>23.610651</v>
+        <v>45.745637</v>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
       <c r="O15" s="0" t="n"/>
       <c r="P15" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55)</t>
         </is>
       </c>
       <c r="Q15" s="0" t="n">
@@ -2055,7 +2055,7 @@
         <v>1.007523</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>66.836309</v>
+        <v>129.495348</v>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
       <c r="O16" s="0" t="n"/>
       <c r="P16" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55)</t>
         </is>
       </c>
       <c r="Q16" s="0" t="n">
@@ -2109,7 +2109,7 @@
         <v>1.007523</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>77.491372</v>
+        <v>85.43423799999999</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
       <c r="O17" s="0" t="n"/>
       <c r="P17" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=6 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q17" s="0" t="n">
@@ -2163,7 +2163,7 @@
         <v>1.109937</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>38.479591</v>
+        <v>74.554208</v>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
       <c r="O18" s="0" t="n"/>
       <c r="P18" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | gold20-20261029: reward +20% | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | gold20-20261029: reward +20% | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55)</t>
         </is>
       </c>
       <c r="Q18" s="0" t="n">
@@ -2217,7 +2217,7 @@
         <v>1.059486</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>25.011736</v>
+        <v>48.460239</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
       <c r="O19" s="0" t="n"/>
       <c r="P19" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55)</t>
         </is>
       </c>
       <c r="Q19" s="0" t="n">
@@ -2271,7 +2271,7 @@
         <v>1.009034</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>70.802449</v>
+        <v>137.179745</v>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
       <c r="O20" s="0" t="n"/>
       <c r="P20" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55)</t>
         </is>
       </c>
       <c r="Q20" s="0" t="n">
@@ -2325,7 +2325,7 @@
         <v>1.009034</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>82.08979600000001</v>
+        <v>90.504</v>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       <c r="O21" s="0" t="n"/>
       <c r="P21" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=7 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q21" s="0" t="n">
@@ -2379,7 +2379,7 @@
         <v>1.111602</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>45.95625</v>
+        <v>89.040234</v>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
       <c r="O22" s="0" t="n"/>
       <c r="P22" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55)</t>
         </is>
       </c>
       <c r="Q22" s="0" t="n">
@@ -2433,7 +2433,7 @@
         <v>1.061075</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>29.871562</v>
+        <v>57.876152</v>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       <c r="O23" s="0" t="n"/>
       <c r="P23" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55)</t>
         </is>
       </c>
       <c r="Q23" s="0" t="n">
@@ -2487,7 +2487,7 @@
         <v>1.010547</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>84.5595</v>
+        <v>163.834031</v>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
       <c r="O24" s="0" t="n"/>
       <c r="P24" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55)</t>
         </is>
       </c>
       <c r="Q24" s="0" t="n">
@@ -2541,7 +2541,7 @@
         <v>1.010547</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>98.04000000000001</v>
+        <v>108.0891</v>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       <c r="O25" s="0" t="n"/>
       <c r="P25" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=8 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q25" s="0" t="n">
@@ -2595,7 +2595,7 @@
         <v>1.11327</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>54.248703</v>
+        <v>105.106862</v>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
       <c r="O26" s="0" t="n"/>
       <c r="P26" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55)</t>
         </is>
       </c>
       <c r="Q26" s="0" t="n">
@@ -2649,7 +2649,7 @@
         <v>1.062666</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>35.261658</v>
+        <v>68.319462</v>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
       <c r="O27" s="0" t="n"/>
       <c r="P27" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55)</t>
         </is>
       </c>
       <c r="Q27" s="0" t="n">
@@ -2703,7 +2703,7 @@
         <v>1.012063</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>99.817617</v>
+        <v>193.396633</v>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
       <c r="O28" s="0" t="n"/>
       <c r="P28" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55)</t>
         </is>
       </c>
       <c r="Q28" s="0" t="n">
@@ -2757,7 +2757,7 @@
         <v>1.012063</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>115.730568</v>
+        <v>127.592951</v>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
       <c r="O29" s="0" t="n"/>
       <c r="P29" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=9 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q29" s="0" t="n">
@@ -2811,7 +2811,7 @@
         <v>1.114939</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>93.32619099999999</v>
+        <v>153.696571</v>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
       <c r="O30" s="0" t="n"/>
       <c r="P30" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W10 ground x0.85</t>
         </is>
       </c>
       <c r="Q30" s="0" t="n">
@@ -2865,7 +2865,7 @@
         <v>1.06426</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>60.662025</v>
+        <v>99.902772</v>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
       <c r="O31" s="0" t="n"/>
       <c r="P31" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W10 ground x0.85</t>
         </is>
       </c>
       <c r="Q31" s="0" t="n">
@@ -2919,7 +2919,7 @@
         <v>1.013581</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>171.720193</v>
+        <v>282.801693</v>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       <c r="O32" s="0" t="n"/>
       <c r="P32" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W10 ground x0.85</t>
         </is>
       </c>
       <c r="Q32" s="0" t="n">
@@ -2973,7 +2973,7 @@
         <v>1.013581</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>199.095876</v>
+        <v>219.503204</v>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
       <c r="O33" s="0" t="n"/>
       <c r="P33" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=10 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q33" s="0" t="n">
@@ -3027,7 +3027,7 @@
         <v>1.116612</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>71.084868</v>
+        <v>117.067892</v>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
       <c r="O34" s="0" t="n"/>
       <c r="P34" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q34" s="0" t="n">
@@ -3081,7 +3081,7 @@
         <v>1.065857</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>46.205166</v>
+        <v>76.094132</v>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
       <c r="O35" s="0" t="n"/>
       <c r="P35" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q35" s="0" t="n">
@@ -3135,7 +3135,7 @@
         <v>1.015102</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>130.796157</v>
+        <v>215.404921</v>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
       <c r="O36" s="0" t="n"/>
       <c r="P36" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q36" s="0" t="n">
@@ -3189,7 +3189,7 @@
         <v>0.8120810000000001</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>241.688551</v>
+        <v>398.030833</v>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
       <c r="O37" s="0" t="n"/>
       <c r="P37" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q37" s="0" t="n">
@@ -3243,7 +3243,7 @@
         <v>1.015102</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>151.64772</v>
+        <v>167.191611</v>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
       <c r="O38" s="0" t="n"/>
       <c r="P38" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=11 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q38" s="0" t="n">
@@ -3297,7 +3297,7 @@
         <v>1.118287</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>68.259739</v>
+        <v>112.415258</v>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
       <c r="O39" s="0" t="n"/>
       <c r="P39" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q39" s="0" t="n">
@@ -3351,7 +3351,7 @@
         <v>1.067456</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>44.368831</v>
+        <v>73.069918</v>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
       <c r="O40" s="0" t="n"/>
       <c r="P40" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q40" s="0" t="n">
@@ -3405,7 +3405,7 @@
         <v>1.016624</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>125.597924</v>
+        <v>206.844081</v>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
       <c r="O41" s="0" t="n"/>
       <c r="P41" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q41" s="0" t="n">
@@ -3459,7 +3459,7 @@
         <v>0.813299</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>232.083117</v>
+        <v>382.211883</v>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
       <c r="O42" s="0" t="n"/>
       <c r="P42" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q42" s="0" t="n">
@@ -3513,7 +3513,7 @@
         <v>1.016624</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>145.62078</v>
+        <v>160.54691</v>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       <c r="O43" s="0" t="n"/>
       <c r="P43" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=12 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q43" s="0" t="n">
@@ -3567,7 +3567,7 @@
         <v>1.119964</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>78.298429</v>
+        <v>128.947725</v>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
       <c r="O44" s="0" t="n"/>
       <c r="P44" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q44" s="0" t="n">
@@ -3621,7 +3621,7 @@
         <v>1.069057</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>50.893979</v>
+        <v>83.816022</v>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
       <c r="O45" s="0" t="n"/>
       <c r="P45" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q45" s="0" t="n">
@@ -3675,7 +3675,7 @@
         <v>1.018149</v>
       </c>
       <c r="D46" s="0" t="n">
-        <v>144.069111</v>
+        <v>237.263818</v>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
       <c r="O46" s="0" t="n"/>
       <c r="P46" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q46" s="0" t="n">
@@ -3729,7 +3729,7 @@
         <v>0.814519</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>266.21466</v>
+        <v>438.422268</v>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
       <c r="O47" s="0" t="n"/>
       <c r="P47" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q47" s="0" t="n">
@@ -3783,7 +3783,7 @@
         <v>1.018149</v>
       </c>
       <c r="D48" s="0" t="n">
-        <v>167.036648</v>
+        <v>184.157904</v>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
       <c r="O48" s="0" t="n"/>
       <c r="P48" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=13 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q48" s="0" t="n">
@@ -3837,7 +3837,7 @@
         <v>1.121644</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>90.25483</v>
+        <v>148.638422</v>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
       <c r="O49" s="0" t="n"/>
       <c r="P49" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q49" s="0" t="n">
@@ -3891,7 +3891,7 @@
         <v>1.07066</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>58.665641</v>
+        <v>96.614977</v>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       <c r="O50" s="0" t="n"/>
       <c r="P50" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q50" s="0" t="n">
@@ -3945,7 +3945,7 @@
         <v>1.019676</v>
       </c>
       <c r="D51" s="0" t="n">
-        <v>166.068887</v>
+        <v>273.494699</v>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
       <c r="O51" s="0" t="n"/>
       <c r="P51" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q51" s="0" t="n">
@@ -3999,7 +3999,7 @@
         <v>0.815741</v>
       </c>
       <c r="D52" s="0" t="n">
-        <v>306.866422</v>
+        <v>505.370639</v>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
       <c r="O52" s="0" t="n"/>
       <c r="P52" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85)</t>
         </is>
       </c>
       <c r="Q52" s="0" t="n">
@@ -4053,7 +4053,7 @@
         <v>1.019676</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>192.543636</v>
+        <v>212.279359</v>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
       <c r="O53" s="0" t="n"/>
       <c r="P53" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=14 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q53" s="0" t="n">
@@ -4107,7 +4107,7 @@
         <v>1.123327</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>147.857144</v>
+        <v>208.19441</v>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
       <c r="O54" s="0" t="n"/>
       <c r="P54" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q54" s="0" t="n">
@@ -4161,7 +4161,7 @@
         <v>1.072266</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>96.10714299999999</v>
+        <v>135.326367</v>
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
       <c r="O55" s="0" t="n"/>
       <c r="P55" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q55" s="0" t="n">
@@ -4215,7 +4215,7 @@
         <v>1.021206</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>272.057143</v>
+        <v>383.077712</v>
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
       <c r="O56" s="0" t="n"/>
       <c r="P56" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q56" s="0" t="n">
@@ -4269,7 +4269,7 @@
         <v>0.8169650000000001</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>502.714284</v>
+        <v>707.860986</v>
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
       <c r="O57" s="0" t="n"/>
       <c r="P57" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q57" s="0" t="n">
@@ -4323,7 +4323,7 @@
         <v>1.021206</v>
       </c>
       <c r="D58" s="0" t="n">
-        <v>315.428572</v>
+        <v>347.760001</v>
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
       <c r="O58" s="0" t="n"/>
       <c r="P58" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=15 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q58" s="0" t="n">
@@ -4377,7 +4377,7 @@
         <v>1.125012</v>
       </c>
       <c r="D59" s="0" t="n">
-        <v>144.948933</v>
+        <v>204.099421</v>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
       <c r="O59" s="0" t="n"/>
       <c r="P59" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q59" s="0" t="n">
@@ -4431,7 +4431,7 @@
         <v>1.073875</v>
       </c>
       <c r="D60" s="0" t="n">
-        <v>94.21680600000001</v>
+        <v>132.664624</v>
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
       <c r="O60" s="0" t="n"/>
       <c r="P60" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q60" s="0" t="n">
@@ -4485,7 +4485,7 @@
         <v>1.022738</v>
       </c>
       <c r="D61" s="0" t="n">
-        <v>266.706037</v>
+        <v>375.542936</v>
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
       <c r="O61" s="0" t="n"/>
       <c r="P61" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q61" s="0" t="n">
@@ -4539,7 +4539,7 @@
         <v>0.81819</v>
       </c>
       <c r="D62" s="0" t="n">
-        <v>492.826374</v>
+        <v>693.938036</v>
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
       <c r="O62" s="0" t="n"/>
       <c r="P62" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q62" s="0" t="n">
@@ -4593,7 +4593,7 @@
         <v>1.022738</v>
       </c>
       <c r="D63" s="0" t="n">
-        <v>309.224392</v>
+        <v>340.919893</v>
       </c>
       <c r="E63" s="0" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
       <c r="O63" s="0" t="n"/>
       <c r="P63" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=16 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q63" s="0" t="n">
@@ -4647,7 +4647,7 @@
         <v>1.126699</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>139.53063</v>
+        <v>196.470027</v>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
       <c r="O64" s="0" t="n"/>
       <c r="P64" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q64" s="0" t="n">
@@ -4701,7 +4701,7 @@
         <v>1.075485</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>90.694909</v>
+        <v>127.705517</v>
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
       <c r="O65" s="0" t="n"/>
       <c r="P65" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q65" s="0" t="n">
@@ -4755,7 +4755,7 @@
         <v>1.024272</v>
       </c>
       <c r="D66" s="0" t="n">
-        <v>256.736358</v>
+        <v>361.50485</v>
       </c>
       <c r="E66" s="0" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
       <c r="O66" s="0" t="n"/>
       <c r="P66" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q66" s="0" t="n">
@@ -4809,7 +4809,7 @@
         <v>0.819418</v>
       </c>
       <c r="D67" s="0" t="n">
-        <v>474.404142</v>
+        <v>667.998094</v>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
       <c r="O67" s="0" t="n"/>
       <c r="P67" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q67" s="0" t="n">
@@ -4863,7 +4863,7 @@
         <v>1.024272</v>
       </c>
       <c r="D68" s="0" t="n">
-        <v>297.665344</v>
+        <v>328.176042</v>
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
       <c r="O68" s="0" t="n"/>
       <c r="P68" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=17 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q68" s="0" t="n">
@@ -4917,7 +4917,7 @@
         <v>1.128389</v>
       </c>
       <c r="D69" s="0" t="n">
-        <v>142.036187</v>
+        <v>199.998048</v>
       </c>
       <c r="E69" s="0" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
       <c r="O69" s="0" t="n"/>
       <c r="P69" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q69" s="0" t="n">
@@ -4971,7 +4971,7 @@
         <v>1.077099</v>
       </c>
       <c r="D70" s="0" t="n">
-        <v>92.323521</v>
+        <v>129.998731</v>
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
       <c r="O70" s="0" t="n"/>
       <c r="P70" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q70" s="0" t="n">
@@ -5025,7 +5025,7 @@
         <v>1.025808</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>261.346583</v>
+        <v>367.996407</v>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
       <c r="O71" s="0" t="n"/>
       <c r="P71" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q71" s="0" t="n">
@@ -5079,7 +5079,7 @@
         <v>0.820647</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>482.923035</v>
+        <v>679.993363</v>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
       <c r="O72" s="0" t="n"/>
       <c r="P72" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q72" s="0" t="n">
@@ -5133,7 +5133,7 @@
         <v>1.025808</v>
       </c>
       <c r="D73" s="0" t="n">
-        <v>303.010532</v>
+        <v>334.069112</v>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
       <c r="O73" s="0" t="n"/>
       <c r="P73" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=18 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q73" s="0" t="n">
@@ -5187,7 +5187,7 @@
         <v>1.130082</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>158.949909</v>
+        <v>223.81389</v>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
       <c r="O74" s="0" t="n"/>
       <c r="P74" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q74" s="0" t="n">
@@ -5241,7 +5241,7 @@
         <v>1.078714</v>
       </c>
       <c r="D75" s="0" t="n">
-        <v>103.317442</v>
+        <v>145.479031</v>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
       <c r="O75" s="0" t="n"/>
       <c r="P75" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q75" s="0" t="n">
@@ -5295,7 +5295,7 @@
         <v>1.027347</v>
       </c>
       <c r="D76" s="0" t="n">
-        <v>292.467832</v>
+        <v>411.817556</v>
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
       <c r="O76" s="0" t="n"/>
       <c r="P76" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q76" s="0" t="n">
@@ -5349,7 +5349,7 @@
         <v>0.821878</v>
       </c>
       <c r="D77" s="0" t="n">
-        <v>540.4296900000001</v>
+        <v>760.967224</v>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
       <c r="O77" s="0" t="n"/>
       <c r="P77" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q77" s="0" t="n">
@@ -5403,7 +5403,7 @@
         <v>1.027347</v>
       </c>
       <c r="D78" s="0" t="n">
-        <v>339.09314</v>
+        <v>373.850187</v>
       </c>
       <c r="E78" s="0" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
       <c r="O78" s="0" t="n"/>
       <c r="P78" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=19 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q78" s="0" t="n">
@@ -5457,7 +5457,7 @@
         <v>1.131777</v>
       </c>
       <c r="D79" s="0" t="n">
-        <v>196.383942</v>
+        <v>276.523933</v>
       </c>
       <c r="E79" s="0" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
       <c r="O79" s="0" t="n"/>
       <c r="P79" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | w20soften-20261029: hp x0.7736 | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | w20soften-20261029: hp x0.7736 | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q79" s="0" t="n">
@@ -5511,7 +5511,7 @@
         <v>1.080332</v>
       </c>
       <c r="D80" s="0" t="n">
-        <v>127.649561</v>
+        <v>179.740554</v>
       </c>
       <c r="E80" s="0" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
       <c r="O80" s="0" t="n"/>
       <c r="P80" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | w20soften-20261029: hp x0.7736 | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | w20soften-20261029: hp x0.7736 | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q80" s="0" t="n">
@@ -5565,7 +5565,7 @@
         <v>1.028888</v>
       </c>
       <c r="D81" s="0" t="n">
-        <v>361.346452</v>
+        <v>508.804034</v>
       </c>
       <c r="E81" s="0" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
       <c r="O81" s="0" t="n"/>
       <c r="P81" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | w20soften-20261029: hp x0.7736 | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | w20soften-20261029: hp x0.7736 | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q81" s="0" t="n">
@@ -5619,7 +5619,7 @@
         <v>0.82311</v>
       </c>
       <c r="D82" s="0" t="n">
-        <v>667.7053990000001</v>
+        <v>940.181366</v>
       </c>
       <c r="E82" s="0" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
       <c r="O82" s="0" t="n"/>
       <c r="P82" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | w20soften-20261029: hp x0.7736 | econneutral-20261030: 0.4948 (was 0.52)</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | w20soften-20261029: hp x0.7736 | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q82" s="0" t="n">
@@ -5673,7 +5673,7 @@
         <v>1.028888</v>
       </c>
       <c r="D83" s="0" t="n">
-        <v>418.952407</v>
+        <v>461.895028</v>
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
       <c r="O83" s="0" t="n"/>
       <c r="P83" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | w20soften-20261029: hp x0.7736</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | w20soften-20261029: hp x0.7736 | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q83" s="0" t="n">
@@ -5727,7 +5727,7 @@
         <v>1.133475</v>
       </c>
       <c r="D84" s="0" t="n">
-        <v>250.453564</v>
+        <v>352.658185</v>
       </c>
       <c r="E84" s="0" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
       <c r="O84" s="0" t="n"/>
       <c r="P84" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q84" s="0" t="n">
@@ -5781,7 +5781,7 @@
         <v>1.081953</v>
       </c>
       <c r="D85" s="0" t="n">
-        <v>162.794817</v>
+        <v>229.227821</v>
       </c>
       <c r="E85" s="0" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
       <c r="O85" s="0" t="n"/>
       <c r="P85" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q85" s="0" t="n">
@@ -5835,7 +5835,7 @@
         <v>1.030431</v>
       </c>
       <c r="D86" s="0" t="n">
-        <v>460.834559</v>
+        <v>648.891062</v>
       </c>
       <c r="E86" s="0" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
       <c r="O86" s="0" t="n"/>
       <c r="P86" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q86" s="0" t="n">
@@ -5889,7 +5889,7 @@
         <v>0.824345</v>
       </c>
       <c r="D87" s="0" t="n">
-        <v>851.542118</v>
+        <v>1199.037828</v>
       </c>
       <c r="E87" s="0" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
       <c r="O87" s="0" t="n"/>
       <c r="P87" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q87" s="0" t="n">
@@ -5943,7 +5943,7 @@
         <v>1.030431</v>
       </c>
       <c r="D88" s="0" t="n">
-        <v>507.585889</v>
+        <v>559.613442</v>
       </c>
       <c r="E88" s="0" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
       <c r="O88" s="0" t="n"/>
       <c r="P88" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95 | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q88" s="0" t="n">
@@ -5997,7 +5997,7 @@
         <v>1.135175</v>
       </c>
       <c r="D89" s="0" t="n">
-        <v>244.375718</v>
+        <v>344.100103</v>
       </c>
       <c r="E89" s="0" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
       <c r="O89" s="0" t="n"/>
       <c r="P89" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q89" s="0" t="n">
@@ -6051,7 +6051,7 @@
         <v>1.083576</v>
       </c>
       <c r="D90" s="0" t="n">
-        <v>158.844216</v>
+        <v>223.665066</v>
       </c>
       <c r="E90" s="0" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
       <c r="O90" s="0" t="n"/>
       <c r="P90" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q90" s="0" t="n">
@@ -6105,7 +6105,7 @@
         <v>1.031977</v>
       </c>
       <c r="D91" s="0" t="n">
-        <v>449.651319</v>
+        <v>633.144186</v>
       </c>
       <c r="E91" s="0" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
       <c r="O91" s="0" t="n"/>
       <c r="P91" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q91" s="0" t="n">
@@ -6159,7 +6159,7 @@
         <v>0.825582</v>
       </c>
       <c r="D92" s="0" t="n">
-        <v>830.877439</v>
+        <v>1169.940346</v>
       </c>
       <c r="E92" s="0" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
       <c r="O92" s="0" t="n"/>
       <c r="P92" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q92" s="0" t="n">
@@ -6213,7 +6213,7 @@
         <v>1.031977</v>
       </c>
       <c r="D93" s="0" t="n">
-        <v>495.268121</v>
+        <v>546.033103</v>
       </c>
       <c r="E93" s="0" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
       <c r="O93" s="0" t="n"/>
       <c r="P93" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95 | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q93" s="0" t="n">
@@ -6267,7 +6267,7 @@
         <v>1.136877</v>
       </c>
       <c r="D94" s="0" t="n">
-        <v>239.569916</v>
+        <v>337.333158</v>
       </c>
       <c r="E94" s="0" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
       <c r="O94" s="0" t="n"/>
       <c r="P94" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q94" s="0" t="n">
@@ -6321,7 +6321,7 @@
         <v>1.085201</v>
       </c>
       <c r="D95" s="0" t="n">
-        <v>155.720445</v>
+        <v>219.266552</v>
       </c>
       <c r="E95" s="0" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
       <c r="O95" s="0" t="n"/>
       <c r="P95" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q95" s="0" t="n">
@@ -6375,7 +6375,7 @@
         <v>1.033525</v>
       </c>
       <c r="D96" s="0" t="n">
-        <v>440.808647</v>
+        <v>620.6930139999999</v>
       </c>
       <c r="E96" s="0" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
       <c r="O96" s="0" t="n"/>
       <c r="P96" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q96" s="0" t="n">
@@ -6429,7 +6429,7 @@
         <v>0.82682</v>
       </c>
       <c r="D97" s="0" t="n">
-        <v>814.5377140000001</v>
+        <v>1146.932738</v>
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
       <c r="O97" s="0" t="n"/>
       <c r="P97" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q97" s="0" t="n">
@@ -6483,7 +6483,7 @@
         <v>1.033525</v>
       </c>
       <c r="D98" s="0" t="n">
-        <v>485.528364</v>
+        <v>535.295021</v>
       </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
       <c r="O98" s="0" t="n"/>
       <c r="P98" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=23 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95 | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q98" s="0" t="n">
@@ -6537,7 +6537,7 @@
         <v>1.138583</v>
       </c>
       <c r="D99" s="0" t="n">
-        <v>248.921001</v>
+        <v>350.500216</v>
       </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
       <c r="O99" s="0" t="n"/>
       <c r="P99" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | gold20-20261029: reward +20% | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1909 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | gold20-20261029: reward +20% | flatdrop-20261029: 0.20/只(角色=normal) | econneutral-20261030: 0.1909 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q99" s="0" t="n">
@@ -6591,7 +6591,7 @@
         <v>1.086829</v>
       </c>
       <c r="D100" s="0" t="n">
-        <v>161.798652</v>
+        <v>227.825143</v>
       </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
       <c r="O100" s="0" t="n"/>
       <c r="P100" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q100" s="0" t="n">
@@ -6645,7 +6645,7 @@
         <v>1.035075</v>
       </c>
       <c r="D101" s="0" t="n">
-        <v>458.014644</v>
+        <v>644.920401</v>
       </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
       <c r="O101" s="0" t="n"/>
       <c r="P101" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q101" s="0" t="n">
@@ -6699,7 +6699,7 @@
         <v>0.82806</v>
       </c>
       <c r="D102" s="0" t="n">
-        <v>846.331407</v>
+        <v>1191.70074</v>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
       <c r="O102" s="0" t="n"/>
       <c r="P102" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52)</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q102" s="0" t="n">
@@ -6753,7 +6753,7 @@
         <v>1.035075</v>
       </c>
       <c r="D103" s="0" t="n">
-        <v>504.479898</v>
+        <v>556.189088</v>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
       <c r="O103" s="0" t="n"/>
       <c r="P103" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=24 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95 | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q103" s="0" t="n">
@@ -6807,7 +6807,7 @@
         <v>1.140291</v>
       </c>
       <c r="D104" s="0" t="n">
-        <v>342.907479</v>
+        <v>482.840521</v>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
       <c r="O104" s="0" t="n"/>
       <c r="P104" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.1903 (was 0.20)</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q104" s="0" t="n">
@@ -6861,7 +6861,7 @@
         <v>1.088459</v>
       </c>
       <c r="D105" s="0" t="n">
-        <v>222.889862</v>
+        <v>313.846339</v>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
       <c r="O105" s="0" t="n"/>
       <c r="P105" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.1522 (was 0.16)</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q105" s="0" t="n">
@@ -6915,7 +6915,7 @@
         <v>1.036628</v>
       </c>
       <c r="D106" s="0" t="n">
-        <v>630.949761</v>
+        <v>888.426557</v>
       </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
       <c r="O106" s="0" t="n"/>
       <c r="P106" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.3045 (was 0.32)</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q106" s="0" t="n">
@@ -6969,7 +6969,7 @@
         <v>0.829302</v>
       </c>
       <c r="D107" s="0" t="n">
-        <v>1165.885428</v>
+        <v>1641.657768</v>
       </c>
       <c r="E107" s="0" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
       <c r="O107" s="0" t="n"/>
       <c r="P107" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.4948 (was 0.52)</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q107" s="0" t="n">
@@ -7023,7 +7023,7 @@
         <v>0.777471</v>
       </c>
       <c r="D108" s="0" t="n">
-        <v>1872.274838</v>
+        <v>2636.309244</v>
       </c>
       <c r="E108" s="0" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
       <c r="O108" s="0" t="n"/>
       <c r="P108" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=123; role=elite; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 1.40/只(角色=elite) | w25soften-20261030: hp x0.80 | econneutral-20261030: 1.3322 (was 1.40)</t>
+          <t>Balance variant; canonical=123; role=elite; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 1.40/只(角色=elite) | w25soften-20261030: hp x0.80 | econneutral-20261030: 1.3322 (was 1.40) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
         </is>
       </c>
       <c r="Q108" s="0" t="n">
@@ -7077,7 +7077,7 @@
         <v>1.036628</v>
       </c>
       <c r="D109" s="0" t="n">
-        <v>694.959158</v>
+        <v>766.192472</v>
       </c>
       <c r="E109" s="0" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
       <c r="O109" s="0" t="n"/>
       <c r="P109" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95 | w25soften-20261030: hp x0.80</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95 | w25soften-20261030: hp x0.80 | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
         </is>
       </c>
       <c r="Q109" s="0" t="n">

--- a/Luban/Config/Datas/Levels/L01/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L01/EnemyData.xlsx
@@ -5673,7 +5673,7 @@
         <v>1.028888</v>
       </c>
       <c r="D83" s="0" t="n">
-        <v>461.895028</v>
+        <v>438.800277</v>
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
       <c r="O83" s="0" t="n"/>
       <c r="P83" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | w20soften-20261029: hp x0.7736 | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=20 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | w20soften-20261029: hp x0.7736 | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05) | airhp-20261031: W20 air x0.95</t>
         </is>
       </c>
       <c r="Q83" s="0" t="n">
@@ -5943,7 +5943,7 @@
         <v>1.030431</v>
       </c>
       <c r="D88" s="0" t="n">
-        <v>559.613442</v>
+        <v>455.808646</v>
       </c>
       <c r="E88" s="0" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
       <c r="O88" s="0" t="n"/>
       <c r="P88" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95 | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=21 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95 | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05) | airhp-20261031: W21 air x0.95 | airhp2-20261031: W21 air x0.95 again | airhp3-20261031: W21 air x0.95 (third) | airhp4-20261031: W21 air x0.95 (fourth)</t>
         </is>
       </c>
       <c r="Q88" s="0" t="n">

--- a/Luban/Config/Datas/Levels/L01/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L01/EnemyData.xlsx
@@ -6213,7 +6213,7 @@
         <v>1.031977</v>
       </c>
       <c r="D93" s="0" t="n">
-        <v>546.033103</v>
+        <v>491.429793</v>
       </c>
       <c r="E93" s="0" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
       <c r="O93" s="0" t="n"/>
       <c r="P93" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95 | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05)</t>
+          <t>Balance variant; canonical=11; role=air; profile=D04; level=1; wave=22 | wavebuff-20261029: hp x2.0, reward per-wave budget | wavebuff2-20261029: hp x2.0 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.36/只(角色=air) | wavegold-air-20261029: hp x0.95 | hp-20261030: ground x1.25, air x1.05 (x1.05) | hp2-20261030: ground x1.55, air x1.05 (x1.05) | airhp-20261101: W22 air x0.90</t>
         </is>
       </c>
       <c r="Q93" s="0" t="n">
@@ -6807,7 +6807,7 @@
         <v>1.140291</v>
       </c>
       <c r="D104" s="0" t="n">
-        <v>482.840521</v>
+        <v>458.698495</v>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
       <c r="O104" s="0" t="n"/>
       <c r="P104" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
+          <t>Balance variant; canonical=18; role=normal; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.20/只(角色=normal) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.1903 (was 0.20) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95 | hp6-20261101: W25 ground x0.95</t>
         </is>
       </c>
       <c r="Q104" s="0" t="n">
@@ -6861,7 +6861,7 @@
         <v>1.088459</v>
       </c>
       <c r="D105" s="0" t="n">
-        <v>313.846339</v>
+        <v>298.154022</v>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
       <c r="O105" s="0" t="n"/>
       <c r="P105" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
+          <t>Balance variant; canonical=84; role=swarm; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.16/只(角色=swarm) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.1522 (was 0.16) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95 | hp6-20261101: W25 ground x0.95</t>
         </is>
       </c>
       <c r="Q105" s="0" t="n">
@@ -6915,7 +6915,7 @@
         <v>1.036628</v>
       </c>
       <c r="D106" s="0" t="n">
-        <v>888.426557</v>
+        <v>844.005229</v>
       </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
       <c r="O106" s="0" t="n"/>
       <c r="P106" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
+          <t>Balance variant; canonical=83; role=medium; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.32/只(角色=medium) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.3045 (was 0.32) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95 | hp6-20261101: W25 ground x0.95</t>
         </is>
       </c>
       <c r="Q106" s="0" t="n">
@@ -6969,7 +6969,7 @@
         <v>0.829302</v>
       </c>
       <c r="D107" s="0" t="n">
-        <v>1641.657768</v>
+        <v>1559.57488</v>
       </c>
       <c r="E107" s="0" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
       <c r="O107" s="0" t="n"/>
       <c r="P107" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
+          <t>Balance variant; canonical=88; role=heavy; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 0.52/只(角色=heavy) | w25soften-20261030: hp x0.80 | econneutral-20261030: 0.4948 (was 0.52) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95 | hp6-20261101: W25 ground x0.95</t>
         </is>
       </c>
       <c r="Q107" s="0" t="n">
@@ -7023,7 +7023,7 @@
         <v>0.777471</v>
       </c>
       <c r="D108" s="0" t="n">
-        <v>2636.309244</v>
+        <v>2504.493782</v>
       </c>
       <c r="E108" s="0" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
       <c r="O108" s="0" t="n"/>
       <c r="P108" s="0" t="inlineStr">
         <is>
-          <t>Balance variant; canonical=123; role=elite; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 1.40/只(角色=elite) | w25soften-20261030: hp x0.80 | econneutral-20261030: 1.3322 (was 1.40) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95</t>
+          <t>Balance variant; canonical=123; role=elite; profile=D04; level=1; wave=25 | wavebuff-20261029: hp x1.5, reward per-wave budget | wavebuff2-20261029: hp x1.5 again, counts x2 again, reward halved-budget | flatdrop-20261029: 1.40/只(角色=elite) | w25soften-20261030: hp x0.80 | econneutral-20261030: 1.3322 (was 1.40) | hp-20261030: ground x1.25, air x1.05 (x1.25) | hp2-20261030: ground x1.55, air x1.05 (x1.55) | hp3-20261030: W11-25 ground x0.85 (ground x0.85) | hp4-20261030: W15-25 ground x0.9 | hp5-20261030: W15-25 ground x0.95 | hp6-20261101: W25 ground x0.95</t>
         </is>
       </c>
       <c r="Q108" s="0" t="n">

--- a/Luban/Config/Datas/Levels/L01/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L01/EnemyData.xlsx
@@ -1947,7 +1947,7 @@
         <v>1.108275</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>70.37790699999999</v>
+        <v>78.823256</v>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>1.057899</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>45.745637</v>
+        <v>51.235113</v>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>1.007523</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>129.495348</v>
+        <v>145.03479</v>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>1.109937</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>74.554208</v>
+        <v>83.500713</v>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>1.059486</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>48.460239</v>
+        <v>54.275468</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>1.009034</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>137.179745</v>
+        <v>153.641314</v>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>1.111602</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>89.040234</v>
+        <v>99.72506199999999</v>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>1.061075</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>57.876152</v>
+        <v>64.82129</v>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>1.010547</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>163.834031</v>
+        <v>183.494115</v>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>1.11327</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>105.106862</v>
+        <v>117.719685</v>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>1.062666</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>68.319462</v>
+        <v>76.517797</v>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>1.012063</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>193.396633</v>
+        <v>216.604229</v>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>1.116612</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>117.067892</v>
+        <v>131.116039</v>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>1.065857</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>76.094132</v>
+        <v>85.22542799999999</v>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>1.015102</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>215.404921</v>
+        <v>241.253512</v>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>0.8120810000000001</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>398.030833</v>
+        <v>445.794533</v>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>1.118287</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>112.415258</v>
+        <v>125.905089</v>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>1.067456</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>73.069918</v>
+        <v>81.838308</v>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>1.016624</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>206.844081</v>
+        <v>231.665371</v>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>0.813299</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>382.211883</v>
+        <v>428.077309</v>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>1.119964</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>128.947725</v>
+        <v>144.421452</v>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>1.069057</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>83.816022</v>
+        <v>93.87394500000001</v>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>1.018149</v>
       </c>
       <c r="D46" s="0" t="n">
-        <v>237.263818</v>
+        <v>265.735476</v>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>0.814519</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>438.422268</v>
+        <v>491.03294</v>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>1.121644</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>148.638422</v>
+        <v>166.475033</v>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>1.07066</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>96.614977</v>
+        <v>108.208774</v>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>1.019676</v>
       </c>
       <c r="D51" s="0" t="n">
-        <v>273.494699</v>
+        <v>306.314063</v>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>0.815741</v>
       </c>
       <c r="D52" s="0" t="n">
-        <v>505.370639</v>
+        <v>566.015116</v>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>1.125012</v>
       </c>
       <c r="D59" s="0" t="n">
-        <v>204.099421</v>
+        <v>228.591352</v>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>1.073875</v>
       </c>
       <c r="D60" s="0" t="n">
-        <v>132.664624</v>
+        <v>148.584379</v>
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>1.022738</v>
       </c>
       <c r="D61" s="0" t="n">
-        <v>375.542936</v>
+        <v>420.608088</v>
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>0.81819</v>
       </c>
       <c r="D62" s="0" t="n">
-        <v>693.938036</v>
+        <v>777.2106</v>
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>1.126699</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>196.470027</v>
+        <v>220.04643</v>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>1.075485</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>127.705517</v>
+        <v>143.030179</v>
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>1.024272</v>
       </c>
       <c r="D66" s="0" t="n">
-        <v>361.50485</v>
+        <v>404.885432</v>
       </c>
       <c r="E66" s="0" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>0.819418</v>
       </c>
       <c r="D67" s="0" t="n">
-        <v>667.998094</v>
+        <v>748.157865</v>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>1.128389</v>
       </c>
       <c r="D69" s="0" t="n">
-        <v>199.998048</v>
+        <v>223.997814</v>
       </c>
       <c r="E69" s="0" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>1.077099</v>
       </c>
       <c r="D70" s="0" t="n">
-        <v>129.998731</v>
+        <v>145.598579</v>
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>1.025808</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>367.996407</v>
+        <v>412.155976</v>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>0.820647</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>679.993363</v>
+        <v>761.592567</v>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>1.130082</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>223.81389</v>
+        <v>250.671557</v>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>1.078714</v>
       </c>
       <c r="D75" s="0" t="n">
-        <v>145.479031</v>
+        <v>162.936515</v>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>1.027347</v>
       </c>
       <c r="D76" s="0" t="n">
-        <v>411.817556</v>
+        <v>461.235663</v>
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>0.821878</v>
       </c>
       <c r="D77" s="0" t="n">
-        <v>760.967224</v>
+        <v>852.283291</v>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>1.133475</v>
       </c>
       <c r="D84" s="0" t="n">
-        <v>352.658185</v>
+        <v>394.977167</v>
       </c>
       <c r="E84" s="0" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>1.081953</v>
       </c>
       <c r="D85" s="0" t="n">
-        <v>229.227821</v>
+        <v>256.73516</v>
       </c>
       <c r="E85" s="0" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>1.030431</v>
       </c>
       <c r="D86" s="0" t="n">
-        <v>648.891062</v>
+        <v>726.757989</v>
       </c>
       <c r="E86" s="0" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>0.824345</v>
       </c>
       <c r="D87" s="0" t="n">
-        <v>1199.037828</v>
+        <v>1342.922367</v>
       </c>
       <c r="E87" s="0" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>1.135175</v>
       </c>
       <c r="D89" s="0" t="n">
-        <v>344.100103</v>
+        <v>385.392115</v>
       </c>
       <c r="E89" s="0" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>1.083576</v>
       </c>
       <c r="D90" s="0" t="n">
-        <v>223.665066</v>
+        <v>250.504874</v>
       </c>
       <c r="E90" s="0" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>1.031977</v>
       </c>
       <c r="D91" s="0" t="n">
-        <v>633.144186</v>
+        <v>709.121488</v>
       </c>
       <c r="E91" s="0" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>0.825582</v>
       </c>
       <c r="D92" s="0" t="n">
-        <v>1169.940346</v>
+        <v>1310.333188</v>
       </c>
       <c r="E92" s="0" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>1.136877</v>
       </c>
       <c r="D94" s="0" t="n">
-        <v>337.333158</v>
+        <v>377.813137</v>
       </c>
       <c r="E94" s="0" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>1.085201</v>
       </c>
       <c r="D95" s="0" t="n">
-        <v>219.266552</v>
+        <v>245.578538</v>
       </c>
       <c r="E95" s="0" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>1.033525</v>
       </c>
       <c r="D96" s="0" t="n">
-        <v>620.6930139999999</v>
+        <v>695.1761760000001</v>
       </c>
       <c r="E96" s="0" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>0.82682</v>
       </c>
       <c r="D97" s="0" t="n">
-        <v>1146.932738</v>
+        <v>1284.564667</v>
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>1.138583</v>
       </c>
       <c r="D99" s="0" t="n">
-        <v>350.500216</v>
+        <v>392.560242</v>
       </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>1.086829</v>
       </c>
       <c r="D100" s="0" t="n">
-        <v>227.825143</v>
+        <v>255.16416</v>
       </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>1.035075</v>
       </c>
       <c r="D101" s="0" t="n">
-        <v>644.920401</v>
+        <v>722.310849</v>
       </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>0.82806</v>
       </c>
       <c r="D102" s="0" t="n">
-        <v>1191.70074</v>
+        <v>1334.704829</v>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>1.140291</v>
       </c>
       <c r="D104" s="0" t="n">
-        <v>458.698495</v>
+        <v>435.76357</v>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>1.088459</v>
       </c>
       <c r="D105" s="0" t="n">
-        <v>298.154022</v>
+        <v>283.246321</v>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>1.036628</v>
       </c>
       <c r="D106" s="0" t="n">
-        <v>844.005229</v>
+        <v>801.804968</v>
       </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>0.829302</v>
       </c>
       <c r="D107" s="0" t="n">
-        <v>1559.57488</v>
+        <v>1481.596136</v>
       </c>
       <c r="E107" s="0" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>0.777471</v>
       </c>
       <c r="D108" s="0" t="n">
-        <v>2504.493782</v>
+        <v>2379.269093</v>
       </c>
       <c r="E108" s="0" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>1.036628</v>
       </c>
       <c r="D109" s="0" t="n">
-        <v>766.192472</v>
+        <v>789.1782459999999</v>
       </c>
       <c r="E109" s="0" t="inlineStr">
         <is>
